--- a/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2767000</v>
+        <v>6187800</v>
       </c>
       <c r="E8" s="3">
-        <v>2764800</v>
+        <v>2785800</v>
       </c>
       <c r="F8" s="3">
-        <v>2529100</v>
+        <v>2783600</v>
       </c>
       <c r="G8" s="3">
-        <v>4924800</v>
+        <v>2546300</v>
       </c>
       <c r="H8" s="3">
-        <v>4275600</v>
+        <v>4958300</v>
       </c>
       <c r="I8" s="3">
-        <v>3669300</v>
+        <v>4304800</v>
       </c>
       <c r="J8" s="3">
+        <v>3694200</v>
+      </c>
+      <c r="K8" s="3">
         <v>2655100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1516900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1159000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>819400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>596700</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>623200</v>
+        <v>1129000</v>
       </c>
       <c r="E9" s="3">
-        <v>634900</v>
+        <v>627400</v>
       </c>
       <c r="F9" s="3">
-        <v>556600</v>
+        <v>639200</v>
       </c>
       <c r="G9" s="3">
-        <v>1017900</v>
+        <v>560400</v>
       </c>
       <c r="H9" s="3">
-        <v>873200</v>
+        <v>1024900</v>
       </c>
       <c r="I9" s="3">
-        <v>645900</v>
+        <v>879200</v>
       </c>
       <c r="J9" s="3">
+        <v>650300</v>
+      </c>
+      <c r="K9" s="3">
         <v>653100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>423600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>331400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>211000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>148900</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2143800</v>
+        <v>5058800</v>
       </c>
       <c r="E10" s="3">
-        <v>2129900</v>
+        <v>2158400</v>
       </c>
       <c r="F10" s="3">
-        <v>1972500</v>
+        <v>2144400</v>
       </c>
       <c r="G10" s="3">
-        <v>3906800</v>
+        <v>1985900</v>
       </c>
       <c r="H10" s="3">
-        <v>3402400</v>
+        <v>3933400</v>
       </c>
       <c r="I10" s="3">
-        <v>3023300</v>
+        <v>3425600</v>
       </c>
       <c r="J10" s="3">
+        <v>3043900</v>
+      </c>
+      <c r="K10" s="3">
         <v>2002000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1093300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>827700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>608500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>447800</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,47 +860,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1151700</v>
+        <v>1684900</v>
       </c>
       <c r="E12" s="3">
-        <v>1241600</v>
+        <v>1159600</v>
       </c>
       <c r="F12" s="3">
-        <v>1058700</v>
+        <v>1250100</v>
       </c>
       <c r="G12" s="3">
-        <v>1473300</v>
+        <v>1065900</v>
       </c>
       <c r="H12" s="3">
-        <v>1328300</v>
+        <v>1483300</v>
       </c>
       <c r="I12" s="3">
-        <v>1140400</v>
+        <v>1337400</v>
       </c>
       <c r="J12" s="3">
+        <v>1148100</v>
+      </c>
+      <c r="K12" s="3">
         <v>1061500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>458900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>366200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>189500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>130800</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -925,48 +941,54 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>131000</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
+        <v>131900</v>
+      </c>
+      <c r="F14" s="3">
         <v>13300</v>
       </c>
-      <c r="F14" s="3">
-        <v>125000</v>
-      </c>
       <c r="G14" s="3">
-        <v>28300</v>
+        <v>125800</v>
       </c>
       <c r="H14" s="3">
-        <v>8700</v>
+        <v>28500</v>
       </c>
       <c r="I14" s="3">
-        <v>188800</v>
+        <v>8800</v>
       </c>
       <c r="J14" s="3">
+        <v>190000</v>
+      </c>
+      <c r="K14" s="3">
         <v>6600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>5400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-600</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,9 +1025,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2885900</v>
+        <v>4613500</v>
       </c>
       <c r="E17" s="3">
-        <v>2972900</v>
+        <v>2905500</v>
       </c>
       <c r="F17" s="3">
-        <v>2850500</v>
+        <v>2993100</v>
       </c>
       <c r="G17" s="3">
-        <v>4257100</v>
+        <v>2869900</v>
       </c>
       <c r="H17" s="3">
-        <v>3924600</v>
+        <v>4286100</v>
       </c>
       <c r="I17" s="3">
-        <v>3293500</v>
+        <v>3951400</v>
       </c>
       <c r="J17" s="3">
+        <v>3315900</v>
+      </c>
+      <c r="K17" s="3">
         <v>2878300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1463900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1188300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>691300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>502800</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-118900</v>
+        <v>1574300</v>
       </c>
       <c r="E18" s="3">
-        <v>-208100</v>
+        <v>-119700</v>
       </c>
       <c r="F18" s="3">
-        <v>-321500</v>
+        <v>-209500</v>
       </c>
       <c r="G18" s="3">
-        <v>667600</v>
+        <v>-323600</v>
       </c>
       <c r="H18" s="3">
-        <v>351000</v>
+        <v>672200</v>
       </c>
       <c r="I18" s="3">
-        <v>375800</v>
+        <v>353400</v>
       </c>
       <c r="J18" s="3">
+        <v>378300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-223200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>53000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-29200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>128200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>93900</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,203 +1145,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>691800</v>
+        <v>197800</v>
       </c>
       <c r="E20" s="3">
-        <v>359100</v>
+        <v>696500</v>
       </c>
       <c r="F20" s="3">
-        <v>389200</v>
+        <v>361600</v>
       </c>
       <c r="G20" s="3">
-        <v>818700</v>
+        <v>391900</v>
       </c>
       <c r="H20" s="3">
-        <v>122500</v>
+        <v>824200</v>
       </c>
       <c r="I20" s="3">
-        <v>257700</v>
+        <v>123300</v>
       </c>
       <c r="J20" s="3">
+        <v>259500</v>
+      </c>
+      <c r="K20" s="3">
         <v>81200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>407400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>76200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>54600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>42500</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>693600</v>
+      <c r="D21" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E21" s="3">
-        <v>292000</v>
+        <v>698600</v>
       </c>
       <c r="F21" s="3">
-        <v>235700</v>
+        <v>294200</v>
       </c>
       <c r="G21" s="3">
-        <v>1637500</v>
+        <v>237600</v>
       </c>
       <c r="H21" s="3">
-        <v>609000</v>
+        <v>1648900</v>
       </c>
       <c r="I21" s="3">
-        <v>755400</v>
+        <v>613400</v>
       </c>
       <c r="J21" s="3">
+        <v>760700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-42800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>504100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>75800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>201200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>150600</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>209100</v>
+        <v>287400</v>
       </c>
       <c r="E22" s="3">
-        <v>216100</v>
+        <v>210500</v>
       </c>
       <c r="F22" s="3">
-        <v>236900</v>
+        <v>217600</v>
       </c>
       <c r="G22" s="3">
-        <v>231600</v>
+        <v>238600</v>
       </c>
       <c r="H22" s="3">
-        <v>208200</v>
+        <v>233100</v>
       </c>
       <c r="I22" s="3">
-        <v>177600</v>
+        <v>209600</v>
       </c>
       <c r="J22" s="3">
+        <v>178800</v>
+      </c>
+      <c r="K22" s="3">
         <v>101100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>42100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8700</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>363800</v>
+        <v>1484700</v>
       </c>
       <c r="E23" s="3">
-        <v>-65000</v>
+        <v>366300</v>
       </c>
       <c r="F23" s="3">
-        <v>-169100</v>
+        <v>-65500</v>
       </c>
       <c r="G23" s="3">
-        <v>1254700</v>
+        <v>-170300</v>
       </c>
       <c r="H23" s="3">
-        <v>265300</v>
+        <v>1263300</v>
       </c>
       <c r="I23" s="3">
-        <v>455900</v>
+        <v>267100</v>
       </c>
       <c r="J23" s="3">
+        <v>459000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-243000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>418300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>174100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>136400</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>94200</v>
+        <v>243300</v>
       </c>
       <c r="E24" s="3">
-        <v>37300</v>
+        <v>94800</v>
       </c>
       <c r="F24" s="3">
-        <v>49000</v>
+        <v>37500</v>
       </c>
       <c r="G24" s="3">
-        <v>240500</v>
+        <v>49400</v>
       </c>
       <c r="H24" s="3">
-        <v>109500</v>
+        <v>242200</v>
       </c>
       <c r="I24" s="3">
-        <v>169700</v>
+        <v>110200</v>
       </c>
       <c r="J24" s="3">
+        <v>170900</v>
+      </c>
+      <c r="K24" s="3">
         <v>66000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>65500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>44700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>42300</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>269700</v>
+        <v>1241400</v>
       </c>
       <c r="E26" s="3">
-        <v>-102300</v>
+        <v>271500</v>
       </c>
       <c r="F26" s="3">
-        <v>-218200</v>
+        <v>-103000</v>
       </c>
       <c r="G26" s="3">
-        <v>1014200</v>
+        <v>-219700</v>
       </c>
       <c r="H26" s="3">
-        <v>155800</v>
+        <v>1021100</v>
       </c>
       <c r="I26" s="3">
-        <v>286100</v>
+        <v>156800</v>
       </c>
       <c r="J26" s="3">
+        <v>288100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-309000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>352900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>129400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>94100</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>193700</v>
+        <v>1378800</v>
       </c>
       <c r="E27" s="3">
-        <v>-75900</v>
+        <v>195000</v>
       </c>
       <c r="F27" s="3">
-        <v>-448300</v>
+        <v>-76500</v>
       </c>
       <c r="G27" s="3">
-        <v>968100</v>
+        <v>-451400</v>
       </c>
       <c r="H27" s="3">
-        <v>153500</v>
+        <v>974700</v>
       </c>
       <c r="I27" s="3">
-        <v>274600</v>
+        <v>154600</v>
       </c>
       <c r="J27" s="3">
+        <v>276400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-197600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>349100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>38300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>151900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>102500</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-691800</v>
+        <v>-197800</v>
       </c>
       <c r="E32" s="3">
-        <v>-359100</v>
+        <v>-696500</v>
       </c>
       <c r="F32" s="3">
-        <v>-389200</v>
+        <v>-361600</v>
       </c>
       <c r="G32" s="3">
-        <v>-818700</v>
+        <v>-391900</v>
       </c>
       <c r="H32" s="3">
-        <v>-122500</v>
+        <v>-824200</v>
       </c>
       <c r="I32" s="3">
-        <v>-257700</v>
+        <v>-123300</v>
       </c>
       <c r="J32" s="3">
+        <v>-259500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-81200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-407400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-76200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-54600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-42500</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>193700</v>
+        <v>1378800</v>
       </c>
       <c r="E33" s="3">
-        <v>-75900</v>
+        <v>195000</v>
       </c>
       <c r="F33" s="3">
-        <v>-448300</v>
+        <v>-76500</v>
       </c>
       <c r="G33" s="3">
-        <v>968100</v>
+        <v>-451400</v>
       </c>
       <c r="H33" s="3">
-        <v>153500</v>
+        <v>974700</v>
       </c>
       <c r="I33" s="3">
-        <v>274600</v>
+        <v>154600</v>
       </c>
       <c r="J33" s="3">
+        <v>276400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-197600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>349100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>38300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>151900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>102500</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>193700</v>
+        <v>1378800</v>
       </c>
       <c r="E35" s="3">
-        <v>-75900</v>
+        <v>195000</v>
       </c>
       <c r="F35" s="3">
-        <v>-448300</v>
+        <v>-76500</v>
       </c>
       <c r="G35" s="3">
-        <v>968100</v>
+        <v>-451400</v>
       </c>
       <c r="H35" s="3">
-        <v>153500</v>
+        <v>974700</v>
       </c>
       <c r="I35" s="3">
-        <v>274600</v>
+        <v>154600</v>
       </c>
       <c r="J35" s="3">
+        <v>276400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-197600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>349100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>38300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>151900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>102500</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,125 +1900,135 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2347400</v>
+        <v>6114500</v>
       </c>
       <c r="E41" s="3">
-        <v>2736500</v>
+        <v>2363300</v>
       </c>
       <c r="F41" s="3">
-        <v>2498700</v>
+        <v>2755100</v>
       </c>
       <c r="G41" s="3">
-        <v>2751000</v>
+        <v>2515700</v>
       </c>
       <c r="H41" s="3">
-        <v>2972900</v>
+        <v>2769700</v>
       </c>
       <c r="I41" s="3">
-        <v>2519000</v>
+        <v>2993100</v>
       </c>
       <c r="J41" s="3">
+        <v>2536100</v>
+      </c>
+      <c r="K41" s="3">
         <v>2545500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2674800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>836300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1085900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>981800</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3527300</v>
+        <v>2467300</v>
       </c>
       <c r="E42" s="3">
-        <v>4082500</v>
+        <v>3551300</v>
       </c>
       <c r="F42" s="3">
-        <v>3427100</v>
+        <v>4110300</v>
       </c>
       <c r="G42" s="3">
-        <v>3183800</v>
+        <v>3450500</v>
       </c>
       <c r="H42" s="3">
-        <v>5074900</v>
+        <v>3205500</v>
       </c>
       <c r="I42" s="3">
-        <v>3884200</v>
+        <v>5109400</v>
       </c>
       <c r="J42" s="3">
+        <v>3910600</v>
+      </c>
+      <c r="K42" s="3">
         <v>1948700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1146400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1015800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>553000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>202100</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1573600</v>
+        <v>1586200</v>
       </c>
       <c r="E43" s="3">
-        <v>1465600</v>
+        <v>1584300</v>
       </c>
       <c r="F43" s="3">
-        <v>1228800</v>
+        <v>1475600</v>
       </c>
       <c r="G43" s="3">
-        <v>1825000</v>
+        <v>1237100</v>
       </c>
       <c r="H43" s="3">
-        <v>1223500</v>
+        <v>1837400</v>
       </c>
       <c r="I43" s="3">
-        <v>1427900</v>
+        <v>1231900</v>
       </c>
       <c r="J43" s="3">
+        <v>1437700</v>
+      </c>
+      <c r="K43" s="3">
         <v>787300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>613200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>306400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>478000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>328400</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1970,204 +2065,222 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1034800</v>
+        <v>2167500</v>
       </c>
       <c r="E45" s="3">
-        <v>843700</v>
+        <v>1041800</v>
       </c>
       <c r="F45" s="3">
-        <v>855500</v>
+        <v>849400</v>
       </c>
       <c r="G45" s="3">
-        <v>1623400</v>
+        <v>861400</v>
       </c>
       <c r="H45" s="3">
-        <v>1691500</v>
+        <v>1634500</v>
       </c>
       <c r="I45" s="3">
-        <v>1906700</v>
+        <v>1703000</v>
       </c>
       <c r="J45" s="3">
+        <v>1919700</v>
+      </c>
+      <c r="K45" s="3">
         <v>1058000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1217200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>536400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>487600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>359800</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>8482900</v>
+        <v>12335500</v>
       </c>
       <c r="E46" s="3">
-        <v>9128200</v>
+        <v>8540700</v>
       </c>
       <c r="F46" s="3">
-        <v>8010200</v>
+        <v>9190300</v>
       </c>
       <c r="G46" s="3">
-        <v>9383200</v>
+        <v>8064700</v>
       </c>
       <c r="H46" s="3">
-        <v>10962700</v>
+        <v>9447100</v>
       </c>
       <c r="I46" s="3">
-        <v>8204400</v>
+        <v>11037400</v>
       </c>
       <c r="J46" s="3">
+        <v>8260300</v>
+      </c>
+      <c r="K46" s="3">
         <v>6339500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5651600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2694000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2185300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1096600</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6931900</v>
+        <v>6859500</v>
       </c>
       <c r="E47" s="3">
-        <v>6211700</v>
+        <v>6979100</v>
       </c>
       <c r="F47" s="3">
-        <v>6623400</v>
+        <v>6254000</v>
       </c>
       <c r="G47" s="3">
-        <v>7086800</v>
+        <v>6668500</v>
       </c>
       <c r="H47" s="3">
-        <v>3742400</v>
+        <v>7135100</v>
       </c>
       <c r="I47" s="3">
-        <v>7128000</v>
+        <v>3767900</v>
       </c>
       <c r="J47" s="3">
+        <v>7176500</v>
+      </c>
+      <c r="K47" s="3">
         <v>2947800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2087000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>950000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>926100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>412400</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>831700</v>
+        <v>804000</v>
       </c>
       <c r="E48" s="3">
-        <v>871400</v>
+        <v>837300</v>
       </c>
       <c r="F48" s="3">
-        <v>934400</v>
+        <v>877400</v>
       </c>
       <c r="G48" s="3">
-        <v>1013800</v>
+        <v>940700</v>
       </c>
       <c r="H48" s="3">
-        <v>810800</v>
+        <v>1020700</v>
       </c>
       <c r="I48" s="3">
-        <v>1550800</v>
+        <v>816300</v>
       </c>
       <c r="J48" s="3">
+        <v>1561400</v>
+      </c>
+      <c r="K48" s="3">
         <v>772100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>773400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>823600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>429900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>322500</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9964100</v>
+        <v>10011700</v>
       </c>
       <c r="E49" s="3">
-        <v>9996900</v>
+        <v>10032000</v>
       </c>
       <c r="F49" s="3">
-        <v>10038000</v>
+        <v>10064900</v>
       </c>
       <c r="G49" s="3">
-        <v>9882700</v>
+        <v>10106300</v>
       </c>
       <c r="H49" s="3">
-        <v>9920100</v>
+        <v>9949900</v>
       </c>
       <c r="I49" s="3">
-        <v>11577100</v>
+        <v>9987600</v>
       </c>
       <c r="J49" s="3">
+        <v>11655900</v>
+      </c>
+      <c r="K49" s="3">
         <v>9671100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7906700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>420500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>272800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>226200</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>258100</v>
+        <v>453800</v>
       </c>
       <c r="E52" s="3">
-        <v>283800</v>
+        <v>259800</v>
       </c>
       <c r="F52" s="3">
-        <v>249400</v>
+        <v>285700</v>
       </c>
       <c r="G52" s="3">
-        <v>272800</v>
+        <v>251100</v>
       </c>
       <c r="H52" s="3">
-        <v>223400</v>
+        <v>274700</v>
       </c>
       <c r="I52" s="3">
-        <v>179800</v>
+        <v>224900</v>
       </c>
       <c r="J52" s="3">
+        <v>181000</v>
+      </c>
+      <c r="K52" s="3">
         <v>210200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>124200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>85100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>60400</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>26468700</v>
+        <v>30464400</v>
       </c>
       <c r="E54" s="3">
-        <v>26491900</v>
+        <v>26648900</v>
       </c>
       <c r="F54" s="3">
-        <v>25855300</v>
+        <v>26672200</v>
       </c>
       <c r="G54" s="3">
-        <v>27639300</v>
+        <v>26031400</v>
       </c>
       <c r="H54" s="3">
-        <v>25659400</v>
+        <v>27827500</v>
       </c>
       <c r="I54" s="3">
-        <v>22402100</v>
+        <v>25834100</v>
       </c>
       <c r="J54" s="3">
+        <v>22554600</v>
+      </c>
+      <c r="K54" s="3">
         <v>19940700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16542900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4923600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3166900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1674400</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,242 +2524,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1045100</v>
+        <v>2288100</v>
       </c>
       <c r="E57" s="3">
-        <v>831100</v>
+        <v>1052200</v>
       </c>
       <c r="F57" s="3">
-        <v>622200</v>
+        <v>836800</v>
       </c>
       <c r="G57" s="3">
-        <v>1697600</v>
+        <v>626400</v>
       </c>
       <c r="H57" s="3">
-        <v>1617500</v>
+        <v>1709100</v>
       </c>
       <c r="I57" s="3">
-        <v>1029900</v>
+        <v>1628500</v>
       </c>
       <c r="J57" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="K57" s="3">
         <v>1005100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>827500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>363500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>249100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>146900</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4511600</v>
+        <v>3594600</v>
       </c>
       <c r="E58" s="3">
-        <v>5504700</v>
+        <v>4542300</v>
       </c>
       <c r="F58" s="3">
-        <v>4648500</v>
+        <v>5542200</v>
       </c>
       <c r="G58" s="3">
-        <v>4213600</v>
+        <v>4680100</v>
       </c>
       <c r="H58" s="3">
-        <v>4972400</v>
+        <v>4242300</v>
       </c>
       <c r="I58" s="3">
-        <v>4505900</v>
+        <v>5006200</v>
       </c>
       <c r="J58" s="3">
+        <v>4536500</v>
+      </c>
+      <c r="K58" s="3">
         <v>951000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1940900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>561700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>117800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>65100</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2899100</v>
+        <v>4183800</v>
       </c>
       <c r="E59" s="3">
-        <v>2807600</v>
+        <v>2918900</v>
       </c>
       <c r="F59" s="3">
-        <v>2788900</v>
+        <v>2826700</v>
       </c>
       <c r="G59" s="3">
-        <v>3641400</v>
+        <v>2807900</v>
       </c>
       <c r="H59" s="3">
-        <v>2907800</v>
+        <v>3666200</v>
       </c>
       <c r="I59" s="3">
-        <v>3300400</v>
+        <v>2927600</v>
       </c>
       <c r="J59" s="3">
+        <v>3322900</v>
+      </c>
+      <c r="K59" s="3">
         <v>2227100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1917900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1080700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>700100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>399900</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8455900</v>
+        <v>10066600</v>
       </c>
       <c r="E60" s="3">
-        <v>9143400</v>
+        <v>8513400</v>
       </c>
       <c r="F60" s="3">
-        <v>8059600</v>
+        <v>9205600</v>
       </c>
       <c r="G60" s="3">
-        <v>9552700</v>
+        <v>8114500</v>
       </c>
       <c r="H60" s="3">
-        <v>9497700</v>
+        <v>9617700</v>
       </c>
       <c r="I60" s="3">
-        <v>5821700</v>
+        <v>9562400</v>
       </c>
       <c r="J60" s="3">
+        <v>5861400</v>
+      </c>
+      <c r="K60" s="3">
         <v>4183100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4686300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2005900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>968700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>561000</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1819500</v>
+        <v>2655100</v>
       </c>
       <c r="E61" s="3">
-        <v>1531700</v>
+        <v>1831900</v>
       </c>
       <c r="F61" s="3">
-        <v>3136900</v>
+        <v>1542100</v>
       </c>
       <c r="G61" s="3">
-        <v>2697700</v>
+        <v>3158300</v>
       </c>
       <c r="H61" s="3">
-        <v>3334100</v>
+        <v>2716000</v>
       </c>
       <c r="I61" s="3">
-        <v>4034700</v>
+        <v>3356800</v>
       </c>
       <c r="J61" s="3">
+        <v>4062200</v>
+      </c>
+      <c r="K61" s="3">
         <v>4784600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2555000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1259600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>860600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>160900</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>587700</v>
+        <v>642400</v>
       </c>
       <c r="E62" s="3">
-        <v>565000</v>
+        <v>591700</v>
       </c>
       <c r="F62" s="3">
-        <v>634500</v>
+        <v>568900</v>
       </c>
       <c r="G62" s="3">
-        <v>635900</v>
+        <v>638800</v>
       </c>
       <c r="H62" s="3">
-        <v>575400</v>
+        <v>640200</v>
       </c>
       <c r="I62" s="3">
-        <v>585900</v>
+        <v>579300</v>
       </c>
       <c r="J62" s="3">
+        <v>589900</v>
+      </c>
+      <c r="K62" s="3">
         <v>545100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>436700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7600</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10964700</v>
+        <v>13478400</v>
       </c>
       <c r="E66" s="3">
-        <v>11347700</v>
+        <v>11039300</v>
       </c>
       <c r="F66" s="3">
-        <v>11998500</v>
+        <v>11424900</v>
       </c>
       <c r="G66" s="3">
-        <v>13356100</v>
+        <v>12080100</v>
       </c>
       <c r="H66" s="3">
-        <v>13685800</v>
+        <v>13447000</v>
       </c>
       <c r="I66" s="3">
-        <v>10687900</v>
+        <v>13779000</v>
       </c>
       <c r="J66" s="3">
+        <v>10760700</v>
+      </c>
+      <c r="K66" s="3">
         <v>10062900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10341400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3420300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1869300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>743200</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>2894200</v>
+      <c r="D72" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E72" s="3">
-        <v>2700400</v>
+        <v>2913900</v>
       </c>
       <c r="F72" s="3">
-        <v>2776400</v>
+        <v>2718800</v>
       </c>
       <c r="G72" s="3">
-        <v>3236300</v>
+        <v>2795300</v>
       </c>
       <c r="H72" s="3">
-        <v>2268200</v>
+        <v>3258400</v>
       </c>
       <c r="I72" s="3">
-        <v>2143100</v>
+        <v>2283700</v>
       </c>
       <c r="J72" s="3">
+        <v>2157700</v>
+      </c>
+      <c r="K72" s="3">
         <v>957900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1164800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>924500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>854500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>662700</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15504000</v>
+        <v>16986000</v>
       </c>
       <c r="E76" s="3">
-        <v>15144200</v>
+        <v>15609600</v>
       </c>
       <c r="F76" s="3">
-        <v>13856900</v>
+        <v>15247300</v>
       </c>
       <c r="G76" s="3">
-        <v>14283300</v>
+        <v>13951200</v>
       </c>
       <c r="H76" s="3">
-        <v>11973600</v>
+        <v>14380500</v>
       </c>
       <c r="I76" s="3">
-        <v>11714200</v>
+        <v>12055100</v>
       </c>
       <c r="J76" s="3">
+        <v>11793900</v>
+      </c>
+      <c r="K76" s="3">
         <v>9877800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6201500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1503300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1297600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>931100</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>193700</v>
+        <v>1378800</v>
       </c>
       <c r="E81" s="3">
-        <v>-75900</v>
+        <v>195000</v>
       </c>
       <c r="F81" s="3">
-        <v>-448300</v>
+        <v>-76500</v>
       </c>
       <c r="G81" s="3">
-        <v>968100</v>
+        <v>-451400</v>
       </c>
       <c r="H81" s="3">
-        <v>153500</v>
+        <v>974700</v>
       </c>
       <c r="I81" s="3">
-        <v>274600</v>
+        <v>154600</v>
       </c>
       <c r="J81" s="3">
+        <v>276400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-197600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>349100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>38300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>151900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>102500</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>120800</v>
+      <c r="D83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E83" s="3">
-        <v>141000</v>
+        <v>121600</v>
       </c>
       <c r="F83" s="3">
-        <v>168000</v>
+        <v>141900</v>
       </c>
       <c r="G83" s="3">
-        <v>151300</v>
+        <v>169200</v>
       </c>
       <c r="H83" s="3">
-        <v>135600</v>
+        <v>152400</v>
       </c>
       <c r="I83" s="3">
-        <v>122000</v>
+        <v>136500</v>
       </c>
       <c r="J83" s="3">
+        <v>122800</v>
+      </c>
+      <c r="K83" s="3">
         <v>99300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>44000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>28700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>18400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14200</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>364700</v>
+      <c r="D89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E89" s="3">
-        <v>341700</v>
+        <v>367200</v>
       </c>
       <c r="F89" s="3">
-        <v>-527900</v>
+        <v>344100</v>
       </c>
       <c r="G89" s="3">
-        <v>1012500</v>
+        <v>-531500</v>
       </c>
       <c r="H89" s="3">
-        <v>982400</v>
+        <v>1019400</v>
       </c>
       <c r="I89" s="3">
-        <v>976100</v>
+        <v>989100</v>
       </c>
       <c r="J89" s="3">
+        <v>982700</v>
+      </c>
+      <c r="K89" s="3">
         <v>728100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>424400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>309000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>373100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>237400</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-68600</v>
+      <c r="D91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E91" s="3">
-        <v>-78700</v>
+        <v>-69100</v>
       </c>
       <c r="F91" s="3">
-        <v>-73500</v>
+        <v>-79200</v>
       </c>
       <c r="G91" s="3">
-        <v>-113600</v>
+        <v>-74000</v>
       </c>
       <c r="H91" s="3">
-        <v>-92900</v>
+        <v>-114400</v>
       </c>
       <c r="I91" s="3">
-        <v>-65100</v>
+        <v>-93600</v>
       </c>
       <c r="J91" s="3">
+        <v>-65500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-94300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-88800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-755500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-99100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-77900</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>156900</v>
+      <c r="D94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E94" s="3">
-        <v>-572800</v>
+        <v>157900</v>
       </c>
       <c r="F94" s="3">
-        <v>-527600</v>
+        <v>-576700</v>
       </c>
       <c r="G94" s="3">
-        <v>-333200</v>
+        <v>-531200</v>
       </c>
       <c r="H94" s="3">
-        <v>-1943900</v>
+        <v>-335500</v>
       </c>
       <c r="I94" s="3">
-        <v>-2103300</v>
+        <v>-1957100</v>
       </c>
       <c r="J94" s="3">
+        <v>-2117600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2737500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-616200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1477600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-621600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-177900</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,8 +3987,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3793,9 +4026,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,124 +4152,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-927500</v>
+      <c r="D100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E100" s="3">
-        <v>541100</v>
+        <v>-933800</v>
       </c>
       <c r="F100" s="3">
-        <v>831900</v>
+        <v>544800</v>
       </c>
       <c r="G100" s="3">
-        <v>-1278100</v>
+        <v>837600</v>
       </c>
       <c r="H100" s="3">
-        <v>1646700</v>
+        <v>-1286800</v>
       </c>
       <c r="I100" s="3">
-        <v>1107300</v>
+        <v>1658000</v>
       </c>
       <c r="J100" s="3">
+        <v>1114800</v>
+      </c>
+      <c r="K100" s="3">
         <v>1697000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2120500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>855400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>808700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-74000</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>31900</v>
+      <c r="D101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E101" s="3">
-        <v>-64200</v>
+        <v>32100</v>
       </c>
       <c r="F101" s="3">
-        <v>-98500</v>
+        <v>-64600</v>
       </c>
       <c r="G101" s="3">
-        <v>42700</v>
+        <v>-99100</v>
       </c>
       <c r="H101" s="3">
-        <v>113100</v>
+        <v>43000</v>
       </c>
       <c r="I101" s="3">
-        <v>-6500</v>
+        <v>113900</v>
       </c>
       <c r="J101" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="K101" s="3">
         <v>204600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>23400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2800</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-374100</v>
+      <c r="D102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E102" s="3">
-        <v>245900</v>
+        <v>-376600</v>
       </c>
       <c r="F102" s="3">
-        <v>-322000</v>
+        <v>247600</v>
       </c>
       <c r="G102" s="3">
-        <v>-556000</v>
+        <v>-324200</v>
       </c>
       <c r="H102" s="3">
-        <v>798400</v>
+        <v>-559800</v>
       </c>
       <c r="I102" s="3">
-        <v>-26500</v>
+        <v>803800</v>
       </c>
       <c r="J102" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-107800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1936900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-289900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>565400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11800</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6187800</v>
+        <v>6149500</v>
       </c>
       <c r="E8" s="3">
-        <v>2785800</v>
+        <v>2768600</v>
       </c>
       <c r="F8" s="3">
-        <v>2783600</v>
+        <v>2766400</v>
       </c>
       <c r="G8" s="3">
-        <v>2546300</v>
+        <v>2530500</v>
       </c>
       <c r="H8" s="3">
-        <v>4958300</v>
+        <v>4927600</v>
       </c>
       <c r="I8" s="3">
-        <v>4304800</v>
+        <v>4278100</v>
       </c>
       <c r="J8" s="3">
-        <v>3694200</v>
+        <v>3671400</v>
       </c>
       <c r="K8" s="3">
         <v>2655100</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1129000</v>
+        <v>1122000</v>
       </c>
       <c r="E9" s="3">
-        <v>627400</v>
+        <v>623500</v>
       </c>
       <c r="F9" s="3">
-        <v>639200</v>
+        <v>635300</v>
       </c>
       <c r="G9" s="3">
-        <v>560400</v>
+        <v>556900</v>
       </c>
       <c r="H9" s="3">
-        <v>1024900</v>
+        <v>1018500</v>
       </c>
       <c r="I9" s="3">
-        <v>879200</v>
+        <v>873700</v>
       </c>
       <c r="J9" s="3">
-        <v>650300</v>
+        <v>646300</v>
       </c>
       <c r="K9" s="3">
         <v>653100</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5058800</v>
+        <v>5027500</v>
       </c>
       <c r="E10" s="3">
-        <v>2158400</v>
+        <v>2145100</v>
       </c>
       <c r="F10" s="3">
-        <v>2144400</v>
+        <v>2131100</v>
       </c>
       <c r="G10" s="3">
-        <v>1985900</v>
+        <v>1973600</v>
       </c>
       <c r="H10" s="3">
-        <v>3933400</v>
+        <v>3909100</v>
       </c>
       <c r="I10" s="3">
-        <v>3425600</v>
+        <v>3404400</v>
       </c>
       <c r="J10" s="3">
-        <v>3043900</v>
+        <v>3025100</v>
       </c>
       <c r="K10" s="3">
         <v>2002000</v>
@@ -867,25 +867,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1684900</v>
+        <v>1674500</v>
       </c>
       <c r="E12" s="3">
-        <v>1159600</v>
+        <v>1152400</v>
       </c>
       <c r="F12" s="3">
-        <v>1250100</v>
+        <v>1242300</v>
       </c>
       <c r="G12" s="3">
-        <v>1065900</v>
+        <v>1059300</v>
       </c>
       <c r="H12" s="3">
-        <v>1483300</v>
+        <v>1474200</v>
       </c>
       <c r="I12" s="3">
-        <v>1337400</v>
+        <v>1329100</v>
       </c>
       <c r="J12" s="3">
-        <v>1148100</v>
+        <v>1141000</v>
       </c>
       <c r="K12" s="3">
         <v>1061500</v>
@@ -950,26 +950,26 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>15900</v>
       </c>
       <c r="E14" s="3">
-        <v>131900</v>
+        <v>131100</v>
       </c>
       <c r="F14" s="3">
         <v>13300</v>
       </c>
       <c r="G14" s="3">
-        <v>125800</v>
+        <v>125000</v>
       </c>
       <c r="H14" s="3">
-        <v>28500</v>
+        <v>28300</v>
       </c>
       <c r="I14" s="3">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="J14" s="3">
-        <v>190000</v>
+        <v>188900</v>
       </c>
       <c r="K14" s="3">
         <v>6600</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4613500</v>
+        <v>4600900</v>
       </c>
       <c r="E17" s="3">
-        <v>2905500</v>
+        <v>2887500</v>
       </c>
       <c r="F17" s="3">
-        <v>2993100</v>
+        <v>2974600</v>
       </c>
       <c r="G17" s="3">
-        <v>2869900</v>
+        <v>2852200</v>
       </c>
       <c r="H17" s="3">
-        <v>4286100</v>
+        <v>4259600</v>
       </c>
       <c r="I17" s="3">
-        <v>3951400</v>
+        <v>3926900</v>
       </c>
       <c r="J17" s="3">
-        <v>3315900</v>
+        <v>3295400</v>
       </c>
       <c r="K17" s="3">
         <v>2878300</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1574300</v>
+        <v>1548600</v>
       </c>
       <c r="E18" s="3">
-        <v>-119700</v>
+        <v>-119000</v>
       </c>
       <c r="F18" s="3">
-        <v>-209500</v>
+        <v>-208200</v>
       </c>
       <c r="G18" s="3">
-        <v>-323600</v>
+        <v>-321600</v>
       </c>
       <c r="H18" s="3">
-        <v>672200</v>
+        <v>668000</v>
       </c>
       <c r="I18" s="3">
-        <v>353400</v>
+        <v>351200</v>
       </c>
       <c r="J18" s="3">
-        <v>378300</v>
+        <v>376000</v>
       </c>
       <c r="K18" s="3">
         <v>-223200</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>197800</v>
+        <v>212500</v>
       </c>
       <c r="E20" s="3">
-        <v>696500</v>
+        <v>692200</v>
       </c>
       <c r="F20" s="3">
-        <v>361600</v>
+        <v>359400</v>
       </c>
       <c r="G20" s="3">
-        <v>391900</v>
+        <v>389500</v>
       </c>
       <c r="H20" s="3">
-        <v>824200</v>
+        <v>819200</v>
       </c>
       <c r="I20" s="3">
-        <v>123300</v>
+        <v>122500</v>
       </c>
       <c r="J20" s="3">
-        <v>259500</v>
+        <v>257900</v>
       </c>
       <c r="K20" s="3">
         <v>81200</v>
@@ -1193,26 +1193,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>10</v>
+      <c r="D21" s="3">
+        <v>1873700</v>
       </c>
       <c r="E21" s="3">
-        <v>698600</v>
+        <v>693800</v>
       </c>
       <c r="F21" s="3">
-        <v>294200</v>
+        <v>291900</v>
       </c>
       <c r="G21" s="3">
-        <v>237600</v>
+        <v>235600</v>
       </c>
       <c r="H21" s="3">
-        <v>1648900</v>
+        <v>1638200</v>
       </c>
       <c r="I21" s="3">
-        <v>613400</v>
+        <v>609100</v>
       </c>
       <c r="J21" s="3">
-        <v>760700</v>
+        <v>755600</v>
       </c>
       <c r="K21" s="3">
         <v>-42800</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>287400</v>
+        <v>285600</v>
       </c>
       <c r="E22" s="3">
-        <v>210500</v>
+        <v>209200</v>
       </c>
       <c r="F22" s="3">
-        <v>217600</v>
+        <v>216200</v>
       </c>
       <c r="G22" s="3">
-        <v>238600</v>
+        <v>237100</v>
       </c>
       <c r="H22" s="3">
-        <v>233100</v>
+        <v>231700</v>
       </c>
       <c r="I22" s="3">
-        <v>209600</v>
+        <v>208300</v>
       </c>
       <c r="J22" s="3">
-        <v>178800</v>
+        <v>177700</v>
       </c>
       <c r="K22" s="3">
         <v>101100</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1484700</v>
+        <v>1475500</v>
       </c>
       <c r="E23" s="3">
-        <v>366300</v>
+        <v>364100</v>
       </c>
       <c r="F23" s="3">
-        <v>-65500</v>
+        <v>-65100</v>
       </c>
       <c r="G23" s="3">
-        <v>-170300</v>
+        <v>-169200</v>
       </c>
       <c r="H23" s="3">
-        <v>1263300</v>
+        <v>1255500</v>
       </c>
       <c r="I23" s="3">
-        <v>267100</v>
+        <v>265400</v>
       </c>
       <c r="J23" s="3">
-        <v>459000</v>
+        <v>456100</v>
       </c>
       <c r="K23" s="3">
         <v>-243000</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>243300</v>
+        <v>241800</v>
       </c>
       <c r="E24" s="3">
-        <v>94800</v>
+        <v>94200</v>
       </c>
       <c r="F24" s="3">
-        <v>37500</v>
+        <v>37300</v>
       </c>
       <c r="G24" s="3">
-        <v>49400</v>
+        <v>49000</v>
       </c>
       <c r="H24" s="3">
-        <v>242200</v>
+        <v>240700</v>
       </c>
       <c r="I24" s="3">
-        <v>110200</v>
+        <v>109600</v>
       </c>
       <c r="J24" s="3">
-        <v>170900</v>
+        <v>169800</v>
       </c>
       <c r="K24" s="3">
         <v>66000</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1241400</v>
+        <v>1233800</v>
       </c>
       <c r="E26" s="3">
-        <v>271500</v>
+        <v>269800</v>
       </c>
       <c r="F26" s="3">
-        <v>-103000</v>
+        <v>-102400</v>
       </c>
       <c r="G26" s="3">
-        <v>-219700</v>
+        <v>-218300</v>
       </c>
       <c r="H26" s="3">
-        <v>1021100</v>
+        <v>1014800</v>
       </c>
       <c r="I26" s="3">
-        <v>156800</v>
+        <v>155800</v>
       </c>
       <c r="J26" s="3">
-        <v>288100</v>
+        <v>286300</v>
       </c>
       <c r="K26" s="3">
         <v>-309000</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1378800</v>
+        <v>1370400</v>
       </c>
       <c r="E27" s="3">
-        <v>195000</v>
+        <v>193800</v>
       </c>
       <c r="F27" s="3">
-        <v>-76500</v>
+        <v>-76000</v>
       </c>
       <c r="G27" s="3">
-        <v>-451400</v>
+        <v>-448600</v>
       </c>
       <c r="H27" s="3">
-        <v>974700</v>
+        <v>968600</v>
       </c>
       <c r="I27" s="3">
-        <v>154600</v>
+        <v>153600</v>
       </c>
       <c r="J27" s="3">
-        <v>276400</v>
+        <v>274700</v>
       </c>
       <c r="K27" s="3">
         <v>-197600</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-197800</v>
+        <v>-212500</v>
       </c>
       <c r="E32" s="3">
-        <v>-696500</v>
+        <v>-692200</v>
       </c>
       <c r="F32" s="3">
-        <v>-361600</v>
+        <v>-359400</v>
       </c>
       <c r="G32" s="3">
-        <v>-391900</v>
+        <v>-389500</v>
       </c>
       <c r="H32" s="3">
-        <v>-824200</v>
+        <v>-819200</v>
       </c>
       <c r="I32" s="3">
-        <v>-123300</v>
+        <v>-122500</v>
       </c>
       <c r="J32" s="3">
-        <v>-259500</v>
+        <v>-257900</v>
       </c>
       <c r="K32" s="3">
         <v>-81200</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1378800</v>
+        <v>1370400</v>
       </c>
       <c r="E33" s="3">
-        <v>195000</v>
+        <v>193800</v>
       </c>
       <c r="F33" s="3">
-        <v>-76500</v>
+        <v>-76000</v>
       </c>
       <c r="G33" s="3">
-        <v>-451400</v>
+        <v>-448600</v>
       </c>
       <c r="H33" s="3">
-        <v>974700</v>
+        <v>968600</v>
       </c>
       <c r="I33" s="3">
-        <v>154600</v>
+        <v>153600</v>
       </c>
       <c r="J33" s="3">
-        <v>276400</v>
+        <v>274700</v>
       </c>
       <c r="K33" s="3">
         <v>-197600</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1378800</v>
+        <v>1370400</v>
       </c>
       <c r="E35" s="3">
-        <v>195000</v>
+        <v>193800</v>
       </c>
       <c r="F35" s="3">
-        <v>-76500</v>
+        <v>-76000</v>
       </c>
       <c r="G35" s="3">
-        <v>-451400</v>
+        <v>-448600</v>
       </c>
       <c r="H35" s="3">
-        <v>974700</v>
+        <v>968600</v>
       </c>
       <c r="I35" s="3">
-        <v>154600</v>
+        <v>153600</v>
       </c>
       <c r="J35" s="3">
-        <v>276400</v>
+        <v>274700</v>
       </c>
       <c r="K35" s="3">
         <v>-197600</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6114500</v>
+        <v>5746400</v>
       </c>
       <c r="E41" s="3">
-        <v>2363300</v>
+        <v>2348700</v>
       </c>
       <c r="F41" s="3">
-        <v>2755100</v>
+        <v>2738100</v>
       </c>
       <c r="G41" s="3">
-        <v>2515700</v>
+        <v>2500100</v>
       </c>
       <c r="H41" s="3">
-        <v>2769700</v>
+        <v>2752600</v>
       </c>
       <c r="I41" s="3">
-        <v>2993100</v>
+        <v>2974600</v>
       </c>
       <c r="J41" s="3">
-        <v>2536100</v>
+        <v>2520500</v>
       </c>
       <c r="K41" s="3">
         <v>2545500</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2467300</v>
+        <v>2452100</v>
       </c>
       <c r="E42" s="3">
-        <v>3551300</v>
+        <v>3529300</v>
       </c>
       <c r="F42" s="3">
-        <v>4110300</v>
+        <v>4084800</v>
       </c>
       <c r="G42" s="3">
-        <v>3450500</v>
+        <v>3429100</v>
       </c>
       <c r="H42" s="3">
-        <v>3205500</v>
+        <v>3185700</v>
       </c>
       <c r="I42" s="3">
-        <v>5109400</v>
+        <v>5077800</v>
       </c>
       <c r="J42" s="3">
-        <v>3910600</v>
+        <v>3886400</v>
       </c>
       <c r="K42" s="3">
         <v>1948700</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1586200</v>
+        <v>2619400</v>
       </c>
       <c r="E43" s="3">
-        <v>1584300</v>
+        <v>1574500</v>
       </c>
       <c r="F43" s="3">
-        <v>1475600</v>
+        <v>1466400</v>
       </c>
       <c r="G43" s="3">
-        <v>1237100</v>
+        <v>1229500</v>
       </c>
       <c r="H43" s="3">
-        <v>1837400</v>
+        <v>1826100</v>
       </c>
       <c r="I43" s="3">
-        <v>1231900</v>
+        <v>1224200</v>
       </c>
       <c r="J43" s="3">
-        <v>1437700</v>
+        <v>1428800</v>
       </c>
       <c r="K43" s="3">
         <v>787300</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2167500</v>
+        <v>1441400</v>
       </c>
       <c r="E45" s="3">
-        <v>1041800</v>
+        <v>1035400</v>
       </c>
       <c r="F45" s="3">
-        <v>849400</v>
+        <v>844200</v>
       </c>
       <c r="G45" s="3">
-        <v>861400</v>
+        <v>856000</v>
       </c>
       <c r="H45" s="3">
-        <v>1634500</v>
+        <v>1624300</v>
       </c>
       <c r="I45" s="3">
-        <v>1703000</v>
+        <v>1692500</v>
       </c>
       <c r="J45" s="3">
-        <v>1919700</v>
+        <v>1907800</v>
       </c>
       <c r="K45" s="3">
         <v>1058000</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12335500</v>
+        <v>12259200</v>
       </c>
       <c r="E46" s="3">
-        <v>8540700</v>
+        <v>8487900</v>
       </c>
       <c r="F46" s="3">
-        <v>9190300</v>
+        <v>9133500</v>
       </c>
       <c r="G46" s="3">
-        <v>8064700</v>
+        <v>8014800</v>
       </c>
       <c r="H46" s="3">
-        <v>9447100</v>
+        <v>9388700</v>
       </c>
       <c r="I46" s="3">
-        <v>11037400</v>
+        <v>10969100</v>
       </c>
       <c r="J46" s="3">
-        <v>8260300</v>
+        <v>8209200</v>
       </c>
       <c r="K46" s="3">
         <v>6339500</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6859500</v>
+        <v>6820500</v>
       </c>
       <c r="E47" s="3">
-        <v>6979100</v>
+        <v>6935900</v>
       </c>
       <c r="F47" s="3">
-        <v>6254000</v>
+        <v>6215300</v>
       </c>
       <c r="G47" s="3">
-        <v>6668500</v>
+        <v>6627300</v>
       </c>
       <c r="H47" s="3">
-        <v>7135100</v>
+        <v>7090900</v>
       </c>
       <c r="I47" s="3">
-        <v>3767900</v>
+        <v>3744600</v>
       </c>
       <c r="J47" s="3">
-        <v>7176500</v>
+        <v>7132100</v>
       </c>
       <c r="K47" s="3">
         <v>2947800</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>804000</v>
+        <v>799000</v>
       </c>
       <c r="E48" s="3">
-        <v>837300</v>
+        <v>832100</v>
       </c>
       <c r="F48" s="3">
-        <v>877400</v>
+        <v>871900</v>
       </c>
       <c r="G48" s="3">
-        <v>940700</v>
+        <v>934900</v>
       </c>
       <c r="H48" s="3">
-        <v>1020700</v>
+        <v>1014400</v>
       </c>
       <c r="I48" s="3">
-        <v>816300</v>
+        <v>811300</v>
       </c>
       <c r="J48" s="3">
-        <v>1561400</v>
+        <v>1551700</v>
       </c>
       <c r="K48" s="3">
         <v>772100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10011700</v>
+        <v>9949700</v>
       </c>
       <c r="E49" s="3">
-        <v>10032000</v>
+        <v>9969900</v>
       </c>
       <c r="F49" s="3">
-        <v>10064900</v>
+        <v>10002600</v>
       </c>
       <c r="G49" s="3">
-        <v>10106300</v>
+        <v>10043800</v>
       </c>
       <c r="H49" s="3">
-        <v>9949900</v>
+        <v>9888400</v>
       </c>
       <c r="I49" s="3">
-        <v>9987600</v>
+        <v>9925800</v>
       </c>
       <c r="J49" s="3">
-        <v>11655900</v>
+        <v>11583800</v>
       </c>
       <c r="K49" s="3">
         <v>9671100</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>453800</v>
+        <v>447500</v>
       </c>
       <c r="E52" s="3">
-        <v>259800</v>
+        <v>258200</v>
       </c>
       <c r="F52" s="3">
-        <v>285700</v>
+        <v>283900</v>
       </c>
       <c r="G52" s="3">
-        <v>251100</v>
+        <v>249500</v>
       </c>
       <c r="H52" s="3">
-        <v>274700</v>
+        <v>273000</v>
       </c>
       <c r="I52" s="3">
-        <v>224900</v>
+        <v>223500</v>
       </c>
       <c r="J52" s="3">
-        <v>181000</v>
+        <v>179900</v>
       </c>
       <c r="K52" s="3">
         <v>210200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>30464400</v>
+        <v>30276000</v>
       </c>
       <c r="E54" s="3">
-        <v>26648900</v>
+        <v>26484000</v>
       </c>
       <c r="F54" s="3">
-        <v>26672200</v>
+        <v>26507200</v>
       </c>
       <c r="G54" s="3">
-        <v>26031400</v>
+        <v>25870300</v>
       </c>
       <c r="H54" s="3">
-        <v>27827500</v>
+        <v>27655300</v>
       </c>
       <c r="I54" s="3">
-        <v>25834100</v>
+        <v>25674300</v>
       </c>
       <c r="J54" s="3">
-        <v>22554600</v>
+        <v>22415100</v>
       </c>
       <c r="K54" s="3">
         <v>19940700</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2288100</v>
+        <v>2274000</v>
       </c>
       <c r="E57" s="3">
-        <v>1052200</v>
+        <v>1045700</v>
       </c>
       <c r="F57" s="3">
-        <v>836800</v>
+        <v>831600</v>
       </c>
       <c r="G57" s="3">
-        <v>626400</v>
+        <v>622500</v>
       </c>
       <c r="H57" s="3">
-        <v>1709100</v>
+        <v>1698500</v>
       </c>
       <c r="I57" s="3">
-        <v>1628500</v>
+        <v>1618400</v>
       </c>
       <c r="J57" s="3">
-        <v>1037000</v>
+        <v>1030500</v>
       </c>
       <c r="K57" s="3">
         <v>1005100</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3594600</v>
+        <v>3572400</v>
       </c>
       <c r="E58" s="3">
-        <v>4542300</v>
+        <v>4514200</v>
       </c>
       <c r="F58" s="3">
-        <v>5542200</v>
+        <v>5507900</v>
       </c>
       <c r="G58" s="3">
-        <v>4680100</v>
+        <v>4651200</v>
       </c>
       <c r="H58" s="3">
-        <v>4242300</v>
+        <v>4216100</v>
       </c>
       <c r="I58" s="3">
-        <v>5006200</v>
+        <v>4975300</v>
       </c>
       <c r="J58" s="3">
-        <v>4536500</v>
+        <v>4508500</v>
       </c>
       <c r="K58" s="3">
         <v>951000</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4183800</v>
+        <v>4157900</v>
       </c>
       <c r="E59" s="3">
-        <v>2918900</v>
+        <v>2900800</v>
       </c>
       <c r="F59" s="3">
-        <v>2826700</v>
+        <v>2809200</v>
       </c>
       <c r="G59" s="3">
-        <v>2807900</v>
+        <v>2790600</v>
       </c>
       <c r="H59" s="3">
-        <v>3666200</v>
+        <v>3643600</v>
       </c>
       <c r="I59" s="3">
-        <v>2927600</v>
+        <v>2909500</v>
       </c>
       <c r="J59" s="3">
-        <v>3322900</v>
+        <v>3302300</v>
       </c>
       <c r="K59" s="3">
         <v>2227100</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10066600</v>
+        <v>10004300</v>
       </c>
       <c r="E60" s="3">
-        <v>8513400</v>
+        <v>8460800</v>
       </c>
       <c r="F60" s="3">
-        <v>9205600</v>
+        <v>9148700</v>
       </c>
       <c r="G60" s="3">
-        <v>8114500</v>
+        <v>8064300</v>
       </c>
       <c r="H60" s="3">
-        <v>9617700</v>
+        <v>9558200</v>
       </c>
       <c r="I60" s="3">
-        <v>9562400</v>
+        <v>9503200</v>
       </c>
       <c r="J60" s="3">
-        <v>5861400</v>
+        <v>5825100</v>
       </c>
       <c r="K60" s="3">
         <v>4183100</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2655100</v>
+        <v>2638700</v>
       </c>
       <c r="E61" s="3">
-        <v>1831900</v>
+        <v>1820500</v>
       </c>
       <c r="F61" s="3">
-        <v>1542100</v>
+        <v>1532600</v>
       </c>
       <c r="G61" s="3">
-        <v>3158300</v>
+        <v>3138700</v>
       </c>
       <c r="H61" s="3">
-        <v>2716000</v>
+        <v>2699200</v>
       </c>
       <c r="I61" s="3">
-        <v>3356800</v>
+        <v>3336000</v>
       </c>
       <c r="J61" s="3">
-        <v>4062200</v>
+        <v>4037000</v>
       </c>
       <c r="K61" s="3">
         <v>4784600</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>642400</v>
+        <v>638400</v>
       </c>
       <c r="E62" s="3">
-        <v>591700</v>
+        <v>588000</v>
       </c>
       <c r="F62" s="3">
-        <v>568900</v>
+        <v>565400</v>
       </c>
       <c r="G62" s="3">
-        <v>638800</v>
+        <v>634800</v>
       </c>
       <c r="H62" s="3">
-        <v>640200</v>
+        <v>636200</v>
       </c>
       <c r="I62" s="3">
-        <v>579300</v>
+        <v>575700</v>
       </c>
       <c r="J62" s="3">
-        <v>589900</v>
+        <v>586200</v>
       </c>
       <c r="K62" s="3">
         <v>545100</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13478400</v>
+        <v>13395000</v>
       </c>
       <c r="E66" s="3">
-        <v>11039300</v>
+        <v>10971000</v>
       </c>
       <c r="F66" s="3">
-        <v>11424900</v>
+        <v>11354300</v>
       </c>
       <c r="G66" s="3">
-        <v>12080100</v>
+        <v>12005400</v>
       </c>
       <c r="H66" s="3">
-        <v>13447000</v>
+        <v>13363800</v>
       </c>
       <c r="I66" s="3">
-        <v>13779000</v>
+        <v>13693700</v>
       </c>
       <c r="J66" s="3">
-        <v>10760700</v>
+        <v>10694100</v>
       </c>
       <c r="K66" s="3">
         <v>10062900</v>
@@ -3136,26 +3136,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>10</v>
+      <c r="D72" s="3">
+        <v>4266100</v>
       </c>
       <c r="E72" s="3">
-        <v>2913900</v>
+        <v>2895800</v>
       </c>
       <c r="F72" s="3">
-        <v>2718800</v>
+        <v>2702000</v>
       </c>
       <c r="G72" s="3">
-        <v>2795300</v>
+        <v>2778000</v>
       </c>
       <c r="H72" s="3">
-        <v>3258400</v>
+        <v>3238200</v>
       </c>
       <c r="I72" s="3">
-        <v>2283700</v>
+        <v>2269600</v>
       </c>
       <c r="J72" s="3">
-        <v>2157700</v>
+        <v>2144400</v>
       </c>
       <c r="K72" s="3">
         <v>957900</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>16986000</v>
+        <v>16880900</v>
       </c>
       <c r="E76" s="3">
-        <v>15609600</v>
+        <v>15513000</v>
       </c>
       <c r="F76" s="3">
-        <v>15247300</v>
+        <v>15153000</v>
       </c>
       <c r="G76" s="3">
-        <v>13951200</v>
+        <v>13864900</v>
       </c>
       <c r="H76" s="3">
-        <v>14380500</v>
+        <v>14291500</v>
       </c>
       <c r="I76" s="3">
-        <v>12055100</v>
+        <v>11980500</v>
       </c>
       <c r="J76" s="3">
-        <v>11793900</v>
+        <v>11720900</v>
       </c>
       <c r="K76" s="3">
         <v>9877800</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1378800</v>
+        <v>1370400</v>
       </c>
       <c r="E81" s="3">
-        <v>195000</v>
+        <v>193800</v>
       </c>
       <c r="F81" s="3">
-        <v>-76500</v>
+        <v>-76000</v>
       </c>
       <c r="G81" s="3">
-        <v>-451400</v>
+        <v>-448600</v>
       </c>
       <c r="H81" s="3">
-        <v>974700</v>
+        <v>968600</v>
       </c>
       <c r="I81" s="3">
-        <v>154600</v>
+        <v>153600</v>
       </c>
       <c r="J81" s="3">
-        <v>276400</v>
+        <v>274700</v>
       </c>
       <c r="K81" s="3">
         <v>-197600</v>
@@ -3495,26 +3495,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>10</v>
+      <c r="D83" s="3">
+        <v>112900</v>
       </c>
       <c r="E83" s="3">
-        <v>121600</v>
+        <v>120900</v>
       </c>
       <c r="F83" s="3">
-        <v>141900</v>
+        <v>141100</v>
       </c>
       <c r="G83" s="3">
-        <v>169200</v>
+        <v>168100</v>
       </c>
       <c r="H83" s="3">
-        <v>152400</v>
+        <v>151400</v>
       </c>
       <c r="I83" s="3">
-        <v>136500</v>
+        <v>135700</v>
       </c>
       <c r="J83" s="3">
-        <v>122800</v>
+        <v>122000</v>
       </c>
       <c r="K83" s="3">
         <v>99300</v>
@@ -3747,26 +3747,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>10</v>
+      <c r="D89" s="3">
+        <v>3040100</v>
       </c>
       <c r="E89" s="3">
-        <v>367200</v>
+        <v>364900</v>
       </c>
       <c r="F89" s="3">
-        <v>344100</v>
+        <v>341900</v>
       </c>
       <c r="G89" s="3">
-        <v>-531500</v>
+        <v>-528200</v>
       </c>
       <c r="H89" s="3">
-        <v>1019400</v>
+        <v>1013100</v>
       </c>
       <c r="I89" s="3">
-        <v>989100</v>
+        <v>983000</v>
       </c>
       <c r="J89" s="3">
-        <v>982700</v>
+        <v>976600</v>
       </c>
       <c r="K89" s="3">
         <v>728100</v>
@@ -3807,26 +3807,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>10</v>
+      <c r="D91" s="3">
+        <v>-83700</v>
       </c>
       <c r="E91" s="3">
-        <v>-69100</v>
+        <v>-68700</v>
       </c>
       <c r="F91" s="3">
-        <v>-79200</v>
+        <v>-78800</v>
       </c>
       <c r="G91" s="3">
-        <v>-74000</v>
+        <v>-73500</v>
       </c>
       <c r="H91" s="3">
-        <v>-114400</v>
+        <v>-113700</v>
       </c>
       <c r="I91" s="3">
-        <v>-93600</v>
+        <v>-93000</v>
       </c>
       <c r="J91" s="3">
-        <v>-65500</v>
+        <v>-65100</v>
       </c>
       <c r="K91" s="3">
         <v>-94300</v>
@@ -3933,26 +3933,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>10</v>
+      <c r="D94" s="3">
+        <v>817800</v>
       </c>
       <c r="E94" s="3">
-        <v>157900</v>
+        <v>156900</v>
       </c>
       <c r="F94" s="3">
-        <v>-576700</v>
+        <v>-573100</v>
       </c>
       <c r="G94" s="3">
-        <v>-531200</v>
+        <v>-527900</v>
       </c>
       <c r="H94" s="3">
-        <v>-335500</v>
+        <v>-333400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1957100</v>
+        <v>-1945000</v>
       </c>
       <c r="J94" s="3">
-        <v>-2117600</v>
+        <v>-2104500</v>
       </c>
       <c r="K94" s="3">
         <v>-2737500</v>
@@ -4161,26 +4161,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>10</v>
+      <c r="D100" s="3">
+        <v>-351900</v>
       </c>
       <c r="E100" s="3">
-        <v>-933800</v>
+        <v>-928000</v>
       </c>
       <c r="F100" s="3">
-        <v>544800</v>
+        <v>541400</v>
       </c>
       <c r="G100" s="3">
-        <v>837600</v>
+        <v>832400</v>
       </c>
       <c r="H100" s="3">
-        <v>-1286800</v>
+        <v>-1278800</v>
       </c>
       <c r="I100" s="3">
-        <v>1658000</v>
+        <v>1647700</v>
       </c>
       <c r="J100" s="3">
-        <v>1114800</v>
+        <v>1107900</v>
       </c>
       <c r="K100" s="3">
         <v>1697000</v>
@@ -4203,26 +4203,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>10</v>
+      <c r="D101" s="3">
+        <v>16600</v>
       </c>
       <c r="E101" s="3">
-        <v>32100</v>
+        <v>31900</v>
       </c>
       <c r="F101" s="3">
-        <v>-64600</v>
+        <v>-64200</v>
       </c>
       <c r="G101" s="3">
-        <v>-99100</v>
+        <v>-98500</v>
       </c>
       <c r="H101" s="3">
-        <v>43000</v>
+        <v>42700</v>
       </c>
       <c r="I101" s="3">
-        <v>113900</v>
+        <v>113200</v>
       </c>
       <c r="J101" s="3">
-        <v>-6600</v>
+        <v>-6500</v>
       </c>
       <c r="K101" s="3">
         <v>204600</v>
@@ -4245,26 +4245,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>10</v>
+      <c r="D102" s="3">
+        <v>3522500</v>
       </c>
       <c r="E102" s="3">
-        <v>-376600</v>
+        <v>-374300</v>
       </c>
       <c r="F102" s="3">
-        <v>247600</v>
+        <v>246100</v>
       </c>
       <c r="G102" s="3">
-        <v>-324200</v>
+        <v>-322200</v>
       </c>
       <c r="H102" s="3">
-        <v>-559800</v>
+        <v>-556400</v>
       </c>
       <c r="I102" s="3">
-        <v>803800</v>
+        <v>798800</v>
       </c>
       <c r="J102" s="3">
-        <v>-26600</v>
+        <v>-26500</v>
       </c>
       <c r="K102" s="3">
         <v>-107800</v>

--- a/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6149500</v>
+        <v>6275000</v>
       </c>
       <c r="E8" s="3">
-        <v>2768600</v>
+        <v>2825100</v>
       </c>
       <c r="F8" s="3">
-        <v>2766400</v>
+        <v>2822800</v>
       </c>
       <c r="G8" s="3">
-        <v>2530500</v>
+        <v>2582200</v>
       </c>
       <c r="H8" s="3">
-        <v>4927600</v>
+        <v>5028200</v>
       </c>
       <c r="I8" s="3">
-        <v>4278100</v>
+        <v>4365400</v>
       </c>
       <c r="J8" s="3">
-        <v>3671400</v>
+        <v>3746300</v>
       </c>
       <c r="K8" s="3">
         <v>2655100</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1122000</v>
+        <v>1144900</v>
       </c>
       <c r="E9" s="3">
-        <v>623500</v>
+        <v>636200</v>
       </c>
       <c r="F9" s="3">
-        <v>635300</v>
+        <v>648200</v>
       </c>
       <c r="G9" s="3">
-        <v>556900</v>
+        <v>568300</v>
       </c>
       <c r="H9" s="3">
-        <v>1018500</v>
+        <v>1039300</v>
       </c>
       <c r="I9" s="3">
-        <v>873700</v>
+        <v>891600</v>
       </c>
       <c r="J9" s="3">
-        <v>646300</v>
+        <v>659500</v>
       </c>
       <c r="K9" s="3">
         <v>653100</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5027500</v>
+        <v>5130100</v>
       </c>
       <c r="E10" s="3">
-        <v>2145100</v>
+        <v>2188900</v>
       </c>
       <c r="F10" s="3">
-        <v>2131100</v>
+        <v>2174600</v>
       </c>
       <c r="G10" s="3">
-        <v>1973600</v>
+        <v>2013900</v>
       </c>
       <c r="H10" s="3">
-        <v>3909100</v>
+        <v>3988900</v>
       </c>
       <c r="I10" s="3">
-        <v>3404400</v>
+        <v>3473900</v>
       </c>
       <c r="J10" s="3">
-        <v>3025100</v>
+        <v>3086800</v>
       </c>
       <c r="K10" s="3">
         <v>2002000</v>
@@ -867,25 +867,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1674500</v>
+        <v>1708700</v>
       </c>
       <c r="E12" s="3">
-        <v>1152400</v>
+        <v>1175900</v>
       </c>
       <c r="F12" s="3">
-        <v>1242300</v>
+        <v>1267700</v>
       </c>
       <c r="G12" s="3">
-        <v>1059300</v>
+        <v>1080900</v>
       </c>
       <c r="H12" s="3">
-        <v>1474200</v>
+        <v>1504300</v>
       </c>
       <c r="I12" s="3">
-        <v>1329100</v>
+        <v>1356200</v>
       </c>
       <c r="J12" s="3">
-        <v>1141000</v>
+        <v>1164300</v>
       </c>
       <c r="K12" s="3">
         <v>1061500</v>
@@ -951,25 +951,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>15900</v>
+        <v>16200</v>
       </c>
       <c r="E14" s="3">
-        <v>131100</v>
+        <v>133800</v>
       </c>
       <c r="F14" s="3">
-        <v>13300</v>
+        <v>13500</v>
       </c>
       <c r="G14" s="3">
-        <v>125000</v>
+        <v>127600</v>
       </c>
       <c r="H14" s="3">
-        <v>28300</v>
+        <v>28900</v>
       </c>
       <c r="I14" s="3">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="J14" s="3">
-        <v>188900</v>
+        <v>192700</v>
       </c>
       <c r="K14" s="3">
         <v>6600</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4600900</v>
+        <v>4694800</v>
       </c>
       <c r="E17" s="3">
-        <v>2887500</v>
+        <v>2946500</v>
       </c>
       <c r="F17" s="3">
-        <v>2974600</v>
+        <v>3035300</v>
       </c>
       <c r="G17" s="3">
-        <v>2852200</v>
+        <v>2910400</v>
       </c>
       <c r="H17" s="3">
-        <v>4259600</v>
+        <v>4346600</v>
       </c>
       <c r="I17" s="3">
-        <v>3926900</v>
+        <v>4007100</v>
       </c>
       <c r="J17" s="3">
-        <v>3295400</v>
+        <v>3362700</v>
       </c>
       <c r="K17" s="3">
         <v>2878300</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1548600</v>
+        <v>1580200</v>
       </c>
       <c r="E18" s="3">
-        <v>-119000</v>
+        <v>-121400</v>
       </c>
       <c r="F18" s="3">
-        <v>-208200</v>
+        <v>-212500</v>
       </c>
       <c r="G18" s="3">
-        <v>-321600</v>
+        <v>-328200</v>
       </c>
       <c r="H18" s="3">
-        <v>668000</v>
+        <v>681600</v>
       </c>
       <c r="I18" s="3">
-        <v>351200</v>
+        <v>358400</v>
       </c>
       <c r="J18" s="3">
-        <v>376000</v>
+        <v>383700</v>
       </c>
       <c r="K18" s="3">
         <v>-223200</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>212500</v>
+        <v>216800</v>
       </c>
       <c r="E20" s="3">
-        <v>692200</v>
+        <v>706300</v>
       </c>
       <c r="F20" s="3">
-        <v>359400</v>
+        <v>366700</v>
       </c>
       <c r="G20" s="3">
-        <v>389500</v>
+        <v>397400</v>
       </c>
       <c r="H20" s="3">
-        <v>819200</v>
+        <v>835900</v>
       </c>
       <c r="I20" s="3">
-        <v>122500</v>
+        <v>125000</v>
       </c>
       <c r="J20" s="3">
-        <v>257900</v>
+        <v>263100</v>
       </c>
       <c r="K20" s="3">
         <v>81200</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1873700</v>
+        <v>1911900</v>
       </c>
       <c r="E21" s="3">
-        <v>693800</v>
+        <v>707900</v>
       </c>
       <c r="F21" s="3">
-        <v>291900</v>
+        <v>297700</v>
       </c>
       <c r="G21" s="3">
-        <v>235600</v>
+        <v>240200</v>
       </c>
       <c r="H21" s="3">
-        <v>1638200</v>
+        <v>1671500</v>
       </c>
       <c r="I21" s="3">
-        <v>609100</v>
+        <v>621400</v>
       </c>
       <c r="J21" s="3">
-        <v>755600</v>
+        <v>770900</v>
       </c>
       <c r="K21" s="3">
         <v>-42800</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>285600</v>
+        <v>291400</v>
       </c>
       <c r="E22" s="3">
-        <v>209200</v>
+        <v>213400</v>
       </c>
       <c r="F22" s="3">
-        <v>216200</v>
+        <v>220600</v>
       </c>
       <c r="G22" s="3">
-        <v>237100</v>
+        <v>241900</v>
       </c>
       <c r="H22" s="3">
-        <v>231700</v>
+        <v>236400</v>
       </c>
       <c r="I22" s="3">
-        <v>208300</v>
+        <v>212600</v>
       </c>
       <c r="J22" s="3">
-        <v>177700</v>
+        <v>181400</v>
       </c>
       <c r="K22" s="3">
         <v>101100</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1475500</v>
+        <v>1505700</v>
       </c>
       <c r="E23" s="3">
-        <v>364100</v>
+        <v>371500</v>
       </c>
       <c r="F23" s="3">
-        <v>-65100</v>
+        <v>-66400</v>
       </c>
       <c r="G23" s="3">
-        <v>-169200</v>
+        <v>-172700</v>
       </c>
       <c r="H23" s="3">
-        <v>1255500</v>
+        <v>1281100</v>
       </c>
       <c r="I23" s="3">
-        <v>265400</v>
+        <v>270800</v>
       </c>
       <c r="J23" s="3">
-        <v>456100</v>
+        <v>465400</v>
       </c>
       <c r="K23" s="3">
         <v>-243000</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>241800</v>
+        <v>246700</v>
       </c>
       <c r="E24" s="3">
-        <v>94200</v>
+        <v>96100</v>
       </c>
       <c r="F24" s="3">
-        <v>37300</v>
+        <v>38100</v>
       </c>
       <c r="G24" s="3">
-        <v>49000</v>
+        <v>50000</v>
       </c>
       <c r="H24" s="3">
-        <v>240700</v>
+        <v>245600</v>
       </c>
       <c r="I24" s="3">
-        <v>109600</v>
+        <v>111800</v>
       </c>
       <c r="J24" s="3">
-        <v>169800</v>
+        <v>173300</v>
       </c>
       <c r="K24" s="3">
         <v>66000</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1233800</v>
+        <v>1259000</v>
       </c>
       <c r="E26" s="3">
-        <v>269800</v>
+        <v>275300</v>
       </c>
       <c r="F26" s="3">
-        <v>-102400</v>
+        <v>-104500</v>
       </c>
       <c r="G26" s="3">
-        <v>-218300</v>
+        <v>-222700</v>
       </c>
       <c r="H26" s="3">
-        <v>1014800</v>
+        <v>1035500</v>
       </c>
       <c r="I26" s="3">
-        <v>155800</v>
+        <v>159000</v>
       </c>
       <c r="J26" s="3">
-        <v>286300</v>
+        <v>292200</v>
       </c>
       <c r="K26" s="3">
         <v>-309000</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1370400</v>
+        <v>1398400</v>
       </c>
       <c r="E27" s="3">
-        <v>193800</v>
+        <v>197800</v>
       </c>
       <c r="F27" s="3">
-        <v>-76000</v>
+        <v>-77500</v>
       </c>
       <c r="G27" s="3">
-        <v>-448600</v>
+        <v>-457800</v>
       </c>
       <c r="H27" s="3">
-        <v>968600</v>
+        <v>988400</v>
       </c>
       <c r="I27" s="3">
-        <v>153600</v>
+        <v>156800</v>
       </c>
       <c r="J27" s="3">
-        <v>274700</v>
+        <v>280300</v>
       </c>
       <c r="K27" s="3">
         <v>-197600</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-212500</v>
+        <v>-216800</v>
       </c>
       <c r="E32" s="3">
-        <v>-692200</v>
+        <v>-706300</v>
       </c>
       <c r="F32" s="3">
-        <v>-359400</v>
+        <v>-366700</v>
       </c>
       <c r="G32" s="3">
-        <v>-389500</v>
+        <v>-397400</v>
       </c>
       <c r="H32" s="3">
-        <v>-819200</v>
+        <v>-835900</v>
       </c>
       <c r="I32" s="3">
-        <v>-122500</v>
+        <v>-125000</v>
       </c>
       <c r="J32" s="3">
-        <v>-257900</v>
+        <v>-263100</v>
       </c>
       <c r="K32" s="3">
         <v>-81200</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1370400</v>
+        <v>1398400</v>
       </c>
       <c r="E33" s="3">
-        <v>193800</v>
+        <v>197800</v>
       </c>
       <c r="F33" s="3">
-        <v>-76000</v>
+        <v>-77500</v>
       </c>
       <c r="G33" s="3">
-        <v>-448600</v>
+        <v>-457800</v>
       </c>
       <c r="H33" s="3">
-        <v>968600</v>
+        <v>988400</v>
       </c>
       <c r="I33" s="3">
-        <v>153600</v>
+        <v>156800</v>
       </c>
       <c r="J33" s="3">
-        <v>274700</v>
+        <v>280300</v>
       </c>
       <c r="K33" s="3">
         <v>-197600</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1370400</v>
+        <v>1398400</v>
       </c>
       <c r="E35" s="3">
-        <v>193800</v>
+        <v>197800</v>
       </c>
       <c r="F35" s="3">
-        <v>-76000</v>
+        <v>-77500</v>
       </c>
       <c r="G35" s="3">
-        <v>-448600</v>
+        <v>-457800</v>
       </c>
       <c r="H35" s="3">
-        <v>968600</v>
+        <v>988400</v>
       </c>
       <c r="I35" s="3">
-        <v>153600</v>
+        <v>156800</v>
       </c>
       <c r="J35" s="3">
-        <v>274700</v>
+        <v>280300</v>
       </c>
       <c r="K35" s="3">
         <v>-197600</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5746400</v>
+        <v>5863600</v>
       </c>
       <c r="E41" s="3">
-        <v>2348700</v>
+        <v>2396700</v>
       </c>
       <c r="F41" s="3">
-        <v>2738100</v>
+        <v>2793900</v>
       </c>
       <c r="G41" s="3">
-        <v>2500100</v>
+        <v>2551200</v>
       </c>
       <c r="H41" s="3">
-        <v>2752600</v>
+        <v>2808700</v>
       </c>
       <c r="I41" s="3">
-        <v>2974600</v>
+        <v>3035300</v>
       </c>
       <c r="J41" s="3">
-        <v>2520500</v>
+        <v>2571900</v>
       </c>
       <c r="K41" s="3">
         <v>2545500</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2452100</v>
+        <v>2502100</v>
       </c>
       <c r="E42" s="3">
-        <v>3529300</v>
+        <v>3601300</v>
       </c>
       <c r="F42" s="3">
-        <v>4084800</v>
+        <v>4168200</v>
       </c>
       <c r="G42" s="3">
-        <v>3429100</v>
+        <v>3499100</v>
       </c>
       <c r="H42" s="3">
-        <v>3185700</v>
+        <v>3250700</v>
       </c>
       <c r="I42" s="3">
-        <v>5077800</v>
+        <v>5181400</v>
       </c>
       <c r="J42" s="3">
-        <v>3886400</v>
+        <v>3965800</v>
       </c>
       <c r="K42" s="3">
         <v>1948700</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2619400</v>
+        <v>2672800</v>
       </c>
       <c r="E43" s="3">
-        <v>1574500</v>
+        <v>1606600</v>
       </c>
       <c r="F43" s="3">
-        <v>1466400</v>
+        <v>1496400</v>
       </c>
       <c r="G43" s="3">
-        <v>1229500</v>
+        <v>1254600</v>
       </c>
       <c r="H43" s="3">
-        <v>1826100</v>
+        <v>1863300</v>
       </c>
       <c r="I43" s="3">
-        <v>1224200</v>
+        <v>1249200</v>
       </c>
       <c r="J43" s="3">
-        <v>1428800</v>
+        <v>1457900</v>
       </c>
       <c r="K43" s="3">
         <v>787300</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1441400</v>
+        <v>1470800</v>
       </c>
       <c r="E45" s="3">
-        <v>1035400</v>
+        <v>1056500</v>
       </c>
       <c r="F45" s="3">
-        <v>844200</v>
+        <v>861400</v>
       </c>
       <c r="G45" s="3">
-        <v>856000</v>
+        <v>873500</v>
       </c>
       <c r="H45" s="3">
-        <v>1624300</v>
+        <v>1657500</v>
       </c>
       <c r="I45" s="3">
-        <v>1692500</v>
+        <v>1727000</v>
       </c>
       <c r="J45" s="3">
-        <v>1907800</v>
+        <v>1946700</v>
       </c>
       <c r="K45" s="3">
         <v>1058000</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12259200</v>
+        <v>12509400</v>
       </c>
       <c r="E46" s="3">
-        <v>8487900</v>
+        <v>8661100</v>
       </c>
       <c r="F46" s="3">
-        <v>9133500</v>
+        <v>9319900</v>
       </c>
       <c r="G46" s="3">
-        <v>8014800</v>
+        <v>8178400</v>
       </c>
       <c r="H46" s="3">
-        <v>9388700</v>
+        <v>9580300</v>
       </c>
       <c r="I46" s="3">
-        <v>10969100</v>
+        <v>11193000</v>
       </c>
       <c r="J46" s="3">
-        <v>8209200</v>
+        <v>8376700</v>
       </c>
       <c r="K46" s="3">
         <v>6339500</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6820500</v>
+        <v>6959800</v>
       </c>
       <c r="E47" s="3">
-        <v>6935900</v>
+        <v>7077500</v>
       </c>
       <c r="F47" s="3">
-        <v>6215300</v>
+        <v>6342100</v>
       </c>
       <c r="G47" s="3">
-        <v>6627300</v>
+        <v>6762500</v>
       </c>
       <c r="H47" s="3">
-        <v>7090900</v>
+        <v>7235700</v>
       </c>
       <c r="I47" s="3">
-        <v>3744600</v>
+        <v>3821000</v>
       </c>
       <c r="J47" s="3">
-        <v>7132100</v>
+        <v>7277700</v>
       </c>
       <c r="K47" s="3">
         <v>2947800</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>799000</v>
+        <v>815300</v>
       </c>
       <c r="E48" s="3">
-        <v>832100</v>
+        <v>849100</v>
       </c>
       <c r="F48" s="3">
-        <v>871900</v>
+        <v>889700</v>
       </c>
       <c r="G48" s="3">
-        <v>934900</v>
+        <v>954000</v>
       </c>
       <c r="H48" s="3">
-        <v>1014400</v>
+        <v>1035100</v>
       </c>
       <c r="I48" s="3">
-        <v>811300</v>
+        <v>827800</v>
       </c>
       <c r="J48" s="3">
-        <v>1551700</v>
+        <v>1583400</v>
       </c>
       <c r="K48" s="3">
         <v>772100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9949700</v>
+        <v>10152800</v>
       </c>
       <c r="E49" s="3">
-        <v>9969900</v>
+        <v>10173400</v>
       </c>
       <c r="F49" s="3">
-        <v>10002600</v>
+        <v>10206800</v>
       </c>
       <c r="G49" s="3">
-        <v>10043800</v>
+        <v>10248800</v>
       </c>
       <c r="H49" s="3">
-        <v>9888400</v>
+        <v>10090200</v>
       </c>
       <c r="I49" s="3">
-        <v>9925800</v>
+        <v>10128400</v>
       </c>
       <c r="J49" s="3">
-        <v>11583800</v>
+        <v>11820200</v>
       </c>
       <c r="K49" s="3">
         <v>9671100</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>447500</v>
+        <v>456600</v>
       </c>
       <c r="E52" s="3">
-        <v>258200</v>
+        <v>263500</v>
       </c>
       <c r="F52" s="3">
-        <v>283900</v>
+        <v>289700</v>
       </c>
       <c r="G52" s="3">
-        <v>249500</v>
+        <v>254600</v>
       </c>
       <c r="H52" s="3">
-        <v>273000</v>
+        <v>278600</v>
       </c>
       <c r="I52" s="3">
-        <v>223500</v>
+        <v>228100</v>
       </c>
       <c r="J52" s="3">
-        <v>179900</v>
+        <v>183600</v>
       </c>
       <c r="K52" s="3">
         <v>210200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>30276000</v>
+        <v>30893900</v>
       </c>
       <c r="E54" s="3">
-        <v>26484000</v>
+        <v>27024600</v>
       </c>
       <c r="F54" s="3">
-        <v>26507200</v>
+        <v>27048300</v>
       </c>
       <c r="G54" s="3">
-        <v>25870300</v>
+        <v>26398400</v>
       </c>
       <c r="H54" s="3">
-        <v>27655300</v>
+        <v>28219800</v>
       </c>
       <c r="I54" s="3">
-        <v>25674300</v>
+        <v>26198300</v>
       </c>
       <c r="J54" s="3">
-        <v>22415100</v>
+        <v>22872600</v>
       </c>
       <c r="K54" s="3">
         <v>19940700</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2274000</v>
+        <v>2320400</v>
       </c>
       <c r="E57" s="3">
-        <v>1045700</v>
+        <v>1067100</v>
       </c>
       <c r="F57" s="3">
-        <v>831600</v>
+        <v>848600</v>
       </c>
       <c r="G57" s="3">
-        <v>622500</v>
+        <v>635300</v>
       </c>
       <c r="H57" s="3">
-        <v>1698500</v>
+        <v>1733200</v>
       </c>
       <c r="I57" s="3">
-        <v>1618400</v>
+        <v>1651400</v>
       </c>
       <c r="J57" s="3">
-        <v>1030500</v>
+        <v>1051600</v>
       </c>
       <c r="K57" s="3">
         <v>1005100</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3572400</v>
+        <v>3645300</v>
       </c>
       <c r="E58" s="3">
-        <v>4514200</v>
+        <v>4606400</v>
       </c>
       <c r="F58" s="3">
-        <v>5507900</v>
+        <v>5620300</v>
       </c>
       <c r="G58" s="3">
-        <v>4651200</v>
+        <v>4746100</v>
       </c>
       <c r="H58" s="3">
-        <v>4216100</v>
+        <v>4302100</v>
       </c>
       <c r="I58" s="3">
-        <v>4975300</v>
+        <v>5076800</v>
       </c>
       <c r="J58" s="3">
-        <v>4508500</v>
+        <v>4600500</v>
       </c>
       <c r="K58" s="3">
         <v>951000</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4157900</v>
+        <v>4242800</v>
       </c>
       <c r="E59" s="3">
-        <v>2900800</v>
+        <v>2960000</v>
       </c>
       <c r="F59" s="3">
-        <v>2809200</v>
+        <v>2866500</v>
       </c>
       <c r="G59" s="3">
-        <v>2790600</v>
+        <v>2847500</v>
       </c>
       <c r="H59" s="3">
-        <v>3643600</v>
+        <v>3717900</v>
       </c>
       <c r="I59" s="3">
-        <v>2909500</v>
+        <v>2968900</v>
       </c>
       <c r="J59" s="3">
-        <v>3302300</v>
+        <v>3369700</v>
       </c>
       <c r="K59" s="3">
         <v>2227100</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10004300</v>
+        <v>10208500</v>
       </c>
       <c r="E60" s="3">
-        <v>8460800</v>
+        <v>8633500</v>
       </c>
       <c r="F60" s="3">
-        <v>9148700</v>
+        <v>9335400</v>
       </c>
       <c r="G60" s="3">
-        <v>8064300</v>
+        <v>8228900</v>
       </c>
       <c r="H60" s="3">
-        <v>9558200</v>
+        <v>9753300</v>
       </c>
       <c r="I60" s="3">
-        <v>9503200</v>
+        <v>9697200</v>
       </c>
       <c r="J60" s="3">
-        <v>5825100</v>
+        <v>5944000</v>
       </c>
       <c r="K60" s="3">
         <v>4183100</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2638700</v>
+        <v>2692600</v>
       </c>
       <c r="E61" s="3">
-        <v>1820500</v>
+        <v>1857700</v>
       </c>
       <c r="F61" s="3">
-        <v>1532600</v>
+        <v>1563900</v>
       </c>
       <c r="G61" s="3">
-        <v>3138700</v>
+        <v>3202800</v>
       </c>
       <c r="H61" s="3">
-        <v>2699200</v>
+        <v>2754300</v>
       </c>
       <c r="I61" s="3">
-        <v>3336000</v>
+        <v>3404100</v>
       </c>
       <c r="J61" s="3">
-        <v>4037000</v>
+        <v>4119400</v>
       </c>
       <c r="K61" s="3">
         <v>4784600</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>638400</v>
+        <v>651500</v>
       </c>
       <c r="E62" s="3">
-        <v>588000</v>
+        <v>600000</v>
       </c>
       <c r="F62" s="3">
-        <v>565400</v>
+        <v>576900</v>
       </c>
       <c r="G62" s="3">
-        <v>634800</v>
+        <v>647800</v>
       </c>
       <c r="H62" s="3">
-        <v>636200</v>
+        <v>649200</v>
       </c>
       <c r="I62" s="3">
-        <v>575700</v>
+        <v>587500</v>
       </c>
       <c r="J62" s="3">
-        <v>586200</v>
+        <v>598200</v>
       </c>
       <c r="K62" s="3">
         <v>545100</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13395000</v>
+        <v>13668400</v>
       </c>
       <c r="E66" s="3">
-        <v>10971000</v>
+        <v>11194900</v>
       </c>
       <c r="F66" s="3">
-        <v>11354300</v>
+        <v>11586000</v>
       </c>
       <c r="G66" s="3">
-        <v>12005400</v>
+        <v>12250500</v>
       </c>
       <c r="H66" s="3">
-        <v>13363800</v>
+        <v>13636600</v>
       </c>
       <c r="I66" s="3">
-        <v>13693700</v>
+        <v>13973200</v>
       </c>
       <c r="J66" s="3">
-        <v>10694100</v>
+        <v>10912400</v>
       </c>
       <c r="K66" s="3">
         <v>10062900</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4266100</v>
+        <v>4353200</v>
       </c>
       <c r="E72" s="3">
-        <v>2895800</v>
+        <v>2954900</v>
       </c>
       <c r="F72" s="3">
-        <v>2702000</v>
+        <v>2757100</v>
       </c>
       <c r="G72" s="3">
-        <v>2778000</v>
+        <v>2834700</v>
       </c>
       <c r="H72" s="3">
-        <v>3238200</v>
+        <v>3304300</v>
       </c>
       <c r="I72" s="3">
-        <v>2269600</v>
+        <v>2315900</v>
       </c>
       <c r="J72" s="3">
-        <v>2144400</v>
+        <v>2188200</v>
       </c>
       <c r="K72" s="3">
         <v>957900</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>16880900</v>
+        <v>17225500</v>
       </c>
       <c r="E76" s="3">
-        <v>15513000</v>
+        <v>15829700</v>
       </c>
       <c r="F76" s="3">
-        <v>15153000</v>
+        <v>15462300</v>
       </c>
       <c r="G76" s="3">
-        <v>13864900</v>
+        <v>14147900</v>
       </c>
       <c r="H76" s="3">
-        <v>14291500</v>
+        <v>14583300</v>
       </c>
       <c r="I76" s="3">
-        <v>11980500</v>
+        <v>12225100</v>
       </c>
       <c r="J76" s="3">
-        <v>11720900</v>
+        <v>11960200</v>
       </c>
       <c r="K76" s="3">
         <v>9877800</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1370400</v>
+        <v>1398400</v>
       </c>
       <c r="E81" s="3">
-        <v>193800</v>
+        <v>197800</v>
       </c>
       <c r="F81" s="3">
-        <v>-76000</v>
+        <v>-77500</v>
       </c>
       <c r="G81" s="3">
-        <v>-448600</v>
+        <v>-457800</v>
       </c>
       <c r="H81" s="3">
-        <v>968600</v>
+        <v>988400</v>
       </c>
       <c r="I81" s="3">
-        <v>153600</v>
+        <v>156800</v>
       </c>
       <c r="J81" s="3">
-        <v>274700</v>
+        <v>280300</v>
       </c>
       <c r="K81" s="3">
         <v>-197600</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>112900</v>
+        <v>115200</v>
       </c>
       <c r="E83" s="3">
-        <v>120900</v>
+        <v>123400</v>
       </c>
       <c r="F83" s="3">
-        <v>141100</v>
+        <v>143900</v>
       </c>
       <c r="G83" s="3">
-        <v>168100</v>
+        <v>171600</v>
       </c>
       <c r="H83" s="3">
-        <v>151400</v>
+        <v>154500</v>
       </c>
       <c r="I83" s="3">
-        <v>135700</v>
+        <v>138400</v>
       </c>
       <c r="J83" s="3">
-        <v>122000</v>
+        <v>124500</v>
       </c>
       <c r="K83" s="3">
         <v>99300</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3040100</v>
+        <v>3102100</v>
       </c>
       <c r="E89" s="3">
-        <v>364900</v>
+        <v>372300</v>
       </c>
       <c r="F89" s="3">
-        <v>341900</v>
+        <v>348900</v>
       </c>
       <c r="G89" s="3">
-        <v>-528200</v>
+        <v>-539000</v>
       </c>
       <c r="H89" s="3">
-        <v>1013100</v>
+        <v>1033800</v>
       </c>
       <c r="I89" s="3">
-        <v>983000</v>
+        <v>1003100</v>
       </c>
       <c r="J89" s="3">
-        <v>976600</v>
+        <v>996600</v>
       </c>
       <c r="K89" s="3">
         <v>728100</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-83700</v>
+        <v>-85400</v>
       </c>
       <c r="E91" s="3">
-        <v>-68700</v>
+        <v>-70100</v>
       </c>
       <c r="F91" s="3">
-        <v>-78800</v>
+        <v>-80400</v>
       </c>
       <c r="G91" s="3">
-        <v>-73500</v>
+        <v>-75000</v>
       </c>
       <c r="H91" s="3">
-        <v>-113700</v>
+        <v>-116000</v>
       </c>
       <c r="I91" s="3">
-        <v>-93000</v>
+        <v>-94900</v>
       </c>
       <c r="J91" s="3">
-        <v>-65100</v>
+        <v>-66400</v>
       </c>
       <c r="K91" s="3">
         <v>-94300</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>817800</v>
+        <v>834500</v>
       </c>
       <c r="E94" s="3">
-        <v>156900</v>
+        <v>160200</v>
       </c>
       <c r="F94" s="3">
-        <v>-573100</v>
+        <v>-584800</v>
       </c>
       <c r="G94" s="3">
-        <v>-527900</v>
+        <v>-538700</v>
       </c>
       <c r="H94" s="3">
-        <v>-333400</v>
+        <v>-340200</v>
       </c>
       <c r="I94" s="3">
-        <v>-1945000</v>
+        <v>-1984700</v>
       </c>
       <c r="J94" s="3">
-        <v>-2104500</v>
+        <v>-2147400</v>
       </c>
       <c r="K94" s="3">
         <v>-2737500</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-351900</v>
+        <v>-359100</v>
       </c>
       <c r="E100" s="3">
-        <v>-928000</v>
+        <v>-947000</v>
       </c>
       <c r="F100" s="3">
-        <v>541400</v>
+        <v>552500</v>
       </c>
       <c r="G100" s="3">
-        <v>832400</v>
+        <v>849400</v>
       </c>
       <c r="H100" s="3">
-        <v>-1278800</v>
+        <v>-1304900</v>
       </c>
       <c r="I100" s="3">
-        <v>1647700</v>
+        <v>1681300</v>
       </c>
       <c r="J100" s="3">
-        <v>1107900</v>
+        <v>1130500</v>
       </c>
       <c r="K100" s="3">
         <v>1697000</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>16600</v>
+        <v>16900</v>
       </c>
       <c r="E101" s="3">
-        <v>31900</v>
+        <v>32600</v>
       </c>
       <c r="F101" s="3">
-        <v>-64200</v>
+        <v>-65600</v>
       </c>
       <c r="G101" s="3">
-        <v>-98500</v>
+        <v>-100500</v>
       </c>
       <c r="H101" s="3">
-        <v>42700</v>
+        <v>43600</v>
       </c>
       <c r="I101" s="3">
-        <v>113200</v>
+        <v>115500</v>
       </c>
       <c r="J101" s="3">
-        <v>-6500</v>
+        <v>-6700</v>
       </c>
       <c r="K101" s="3">
         <v>204600</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3522500</v>
+        <v>3594400</v>
       </c>
       <c r="E102" s="3">
-        <v>-374300</v>
+        <v>-381900</v>
       </c>
       <c r="F102" s="3">
-        <v>246100</v>
+        <v>251100</v>
       </c>
       <c r="G102" s="3">
-        <v>-322200</v>
+        <v>-328800</v>
       </c>
       <c r="H102" s="3">
-        <v>-556400</v>
+        <v>-567700</v>
       </c>
       <c r="I102" s="3">
-        <v>798800</v>
+        <v>815100</v>
       </c>
       <c r="J102" s="3">
-        <v>-26500</v>
+        <v>-27000</v>
       </c>
       <c r="K102" s="3">
         <v>-107800</v>

--- a/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6275000</v>
+        <v>6277100</v>
       </c>
       <c r="E8" s="3">
-        <v>2825100</v>
+        <v>2905400</v>
       </c>
       <c r="F8" s="3">
-        <v>2822800</v>
+        <v>3151900</v>
       </c>
       <c r="G8" s="3">
-        <v>2582200</v>
+        <v>2805500</v>
       </c>
       <c r="H8" s="3">
-        <v>5028200</v>
+        <v>5122300</v>
       </c>
       <c r="I8" s="3">
-        <v>4365400</v>
+        <v>4502200</v>
       </c>
       <c r="J8" s="3">
-        <v>3746300</v>
+        <v>4118200</v>
       </c>
       <c r="K8" s="3">
         <v>2655100</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1144900</v>
+        <v>1145300</v>
       </c>
       <c r="E9" s="3">
-        <v>636200</v>
+        <v>654300</v>
       </c>
       <c r="F9" s="3">
-        <v>648200</v>
+        <v>723800</v>
       </c>
       <c r="G9" s="3">
-        <v>568300</v>
+        <v>617400</v>
       </c>
       <c r="H9" s="3">
-        <v>1039300</v>
+        <v>1058800</v>
       </c>
       <c r="I9" s="3">
-        <v>891600</v>
+        <v>919500</v>
       </c>
       <c r="J9" s="3">
-        <v>659500</v>
+        <v>719000</v>
       </c>
       <c r="K9" s="3">
         <v>653100</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5130100</v>
+        <v>5131800</v>
       </c>
       <c r="E10" s="3">
-        <v>2188900</v>
+        <v>2251100</v>
       </c>
       <c r="F10" s="3">
-        <v>2174600</v>
+        <v>2428100</v>
       </c>
       <c r="G10" s="3">
-        <v>2013900</v>
+        <v>2188100</v>
       </c>
       <c r="H10" s="3">
-        <v>3988900</v>
+        <v>4063500</v>
       </c>
       <c r="I10" s="3">
-        <v>3473900</v>
+        <v>3582700</v>
       </c>
       <c r="J10" s="3">
-        <v>3086800</v>
+        <v>3399300</v>
       </c>
       <c r="K10" s="3">
         <v>2002000</v>
@@ -867,25 +867,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1708700</v>
+        <v>1709200</v>
       </c>
       <c r="E12" s="3">
-        <v>1175900</v>
+        <v>1209300</v>
       </c>
       <c r="F12" s="3">
-        <v>1267700</v>
+        <v>1415500</v>
       </c>
       <c r="G12" s="3">
-        <v>1080900</v>
+        <v>1174400</v>
       </c>
       <c r="H12" s="3">
-        <v>1504300</v>
+        <v>1532400</v>
       </c>
       <c r="I12" s="3">
-        <v>1356200</v>
+        <v>1398700</v>
       </c>
       <c r="J12" s="3">
-        <v>1164300</v>
+        <v>1269300</v>
       </c>
       <c r="K12" s="3">
         <v>1061500</v>
@@ -951,25 +951,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>16200</v>
+        <v>141400</v>
       </c>
       <c r="E14" s="3">
-        <v>133800</v>
+        <v>-313900</v>
       </c>
       <c r="F14" s="3">
-        <v>13500</v>
+        <v>-54600</v>
       </c>
       <c r="G14" s="3">
-        <v>127600</v>
+        <v>65400</v>
       </c>
       <c r="H14" s="3">
-        <v>28900</v>
+        <v>-573900</v>
       </c>
       <c r="I14" s="3">
-        <v>8900</v>
+        <v>246400</v>
       </c>
       <c r="J14" s="3">
-        <v>192700</v>
+        <v>-5800</v>
       </c>
       <c r="K14" s="3">
         <v>6600</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>114800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>126400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>160200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>186000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>142300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>135200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4694800</v>
+        <v>4680100</v>
       </c>
       <c r="E17" s="3">
-        <v>2946500</v>
+        <v>2892600</v>
       </c>
       <c r="F17" s="3">
-        <v>3035300</v>
+        <v>3374100</v>
       </c>
       <c r="G17" s="3">
-        <v>2910400</v>
+        <v>3023500</v>
       </c>
       <c r="H17" s="3">
-        <v>4346600</v>
+        <v>4398500</v>
       </c>
       <c r="I17" s="3">
-        <v>4007100</v>
+        <v>4123500</v>
       </c>
       <c r="J17" s="3">
-        <v>3362700</v>
+        <v>3665900</v>
       </c>
       <c r="K17" s="3">
         <v>2878300</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1580200</v>
+        <v>1597000</v>
       </c>
       <c r="E18" s="3">
-        <v>-121400</v>
+        <v>12800</v>
       </c>
       <c r="F18" s="3">
-        <v>-212500</v>
+        <v>-222100</v>
       </c>
       <c r="G18" s="3">
-        <v>-328200</v>
+        <v>-218000</v>
       </c>
       <c r="H18" s="3">
-        <v>681600</v>
+        <v>723800</v>
       </c>
       <c r="I18" s="3">
-        <v>358400</v>
+        <v>378800</v>
       </c>
       <c r="J18" s="3">
-        <v>383700</v>
+        <v>452300</v>
       </c>
       <c r="K18" s="3">
         <v>-223200</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>216800</v>
+        <v>-173600</v>
       </c>
       <c r="E20" s="3">
-        <v>706300</v>
+        <v>114400</v>
       </c>
       <c r="F20" s="3">
-        <v>366700</v>
+        <v>-19200</v>
       </c>
       <c r="G20" s="3">
-        <v>397400</v>
+        <v>235100</v>
       </c>
       <c r="H20" s="3">
-        <v>835900</v>
+        <v>102400</v>
       </c>
       <c r="I20" s="3">
-        <v>125000</v>
+        <v>-85500</v>
       </c>
       <c r="J20" s="3">
-        <v>263100</v>
+        <v>-119300</v>
       </c>
       <c r="K20" s="3">
         <v>81200</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1911900</v>
+        <v>1885400</v>
       </c>
       <c r="E21" s="3">
-        <v>707900</v>
+        <v>24800</v>
       </c>
       <c r="F21" s="3">
-        <v>297700</v>
+        <v>-42700</v>
       </c>
       <c r="G21" s="3">
-        <v>240200</v>
+        <v>-267100</v>
       </c>
       <c r="H21" s="3">
-        <v>1671500</v>
+        <v>778400</v>
       </c>
       <c r="I21" s="3">
-        <v>621400</v>
+        <v>606600</v>
       </c>
       <c r="J21" s="3">
-        <v>770900</v>
+        <v>706800</v>
       </c>
       <c r="K21" s="3">
         <v>-42800</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>291400</v>
+        <v>291500</v>
       </c>
       <c r="E22" s="3">
-        <v>213400</v>
+        <v>219500</v>
       </c>
       <c r="F22" s="3">
-        <v>220600</v>
+        <v>246400</v>
       </c>
       <c r="G22" s="3">
-        <v>241900</v>
+        <v>262800</v>
       </c>
       <c r="H22" s="3">
-        <v>236400</v>
+        <v>240800</v>
       </c>
       <c r="I22" s="3">
-        <v>212600</v>
+        <v>219300</v>
       </c>
       <c r="J22" s="3">
-        <v>181400</v>
+        <v>197600</v>
       </c>
       <c r="K22" s="3">
         <v>101100</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1505700</v>
+        <v>1657300</v>
       </c>
       <c r="E23" s="3">
-        <v>371500</v>
+        <v>297100</v>
       </c>
       <c r="F23" s="3">
-        <v>-66400</v>
+        <v>-59000</v>
       </c>
       <c r="G23" s="3">
-        <v>-172700</v>
+        <v>-446300</v>
       </c>
       <c r="H23" s="3">
-        <v>1281100</v>
+        <v>1255200</v>
       </c>
       <c r="I23" s="3">
-        <v>270800</v>
+        <v>274700</v>
       </c>
       <c r="J23" s="3">
-        <v>465400</v>
+        <v>531600</v>
       </c>
       <c r="K23" s="3">
         <v>-243000</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>246700</v>
+        <v>246800</v>
       </c>
       <c r="E24" s="3">
-        <v>96100</v>
+        <v>98900</v>
       </c>
       <c r="F24" s="3">
-        <v>38100</v>
+        <v>42500</v>
       </c>
       <c r="G24" s="3">
-        <v>50000</v>
+        <v>54400</v>
       </c>
       <c r="H24" s="3">
-        <v>245600</v>
+        <v>250200</v>
       </c>
       <c r="I24" s="3">
-        <v>111800</v>
+        <v>115300</v>
       </c>
       <c r="J24" s="3">
-        <v>173300</v>
+        <v>197500</v>
       </c>
       <c r="K24" s="3">
         <v>66000</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1259000</v>
+        <v>1410500</v>
       </c>
       <c r="E26" s="3">
-        <v>275300</v>
+        <v>198200</v>
       </c>
       <c r="F26" s="3">
-        <v>-104500</v>
+        <v>-101500</v>
       </c>
       <c r="G26" s="3">
-        <v>-222700</v>
+        <v>-500700</v>
       </c>
       <c r="H26" s="3">
-        <v>1035500</v>
+        <v>1005000</v>
       </c>
       <c r="I26" s="3">
-        <v>159000</v>
+        <v>159400</v>
       </c>
       <c r="J26" s="3">
-        <v>292200</v>
+        <v>334100</v>
       </c>
       <c r="K26" s="3">
         <v>-309000</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1398400</v>
+        <v>1398700</v>
       </c>
       <c r="E27" s="3">
-        <v>197800</v>
+        <v>203400</v>
       </c>
       <c r="F27" s="3">
-        <v>-77500</v>
+        <v>-86600</v>
       </c>
       <c r="G27" s="3">
-        <v>-457800</v>
+        <v>-497400</v>
       </c>
       <c r="H27" s="3">
-        <v>988400</v>
+        <v>1006900</v>
       </c>
       <c r="I27" s="3">
-        <v>156800</v>
+        <v>161700</v>
       </c>
       <c r="J27" s="3">
-        <v>280300</v>
+        <v>331200</v>
       </c>
       <c r="K27" s="3">
         <v>-197600</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-216800</v>
+        <v>173600</v>
       </c>
       <c r="E32" s="3">
-        <v>-706300</v>
+        <v>-114400</v>
       </c>
       <c r="F32" s="3">
-        <v>-366700</v>
+        <v>19200</v>
       </c>
       <c r="G32" s="3">
-        <v>-397400</v>
+        <v>-235100</v>
       </c>
       <c r="H32" s="3">
-        <v>-835900</v>
+        <v>-102400</v>
       </c>
       <c r="I32" s="3">
-        <v>-125000</v>
+        <v>85500</v>
       </c>
       <c r="J32" s="3">
-        <v>-263100</v>
+        <v>119300</v>
       </c>
       <c r="K32" s="3">
         <v>-81200</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1398400</v>
+        <v>1398700</v>
       </c>
       <c r="E33" s="3">
-        <v>197800</v>
+        <v>203400</v>
       </c>
       <c r="F33" s="3">
-        <v>-77500</v>
+        <v>-86600</v>
       </c>
       <c r="G33" s="3">
-        <v>-457800</v>
+        <v>-497400</v>
       </c>
       <c r="H33" s="3">
-        <v>988400</v>
+        <v>1006900</v>
       </c>
       <c r="I33" s="3">
-        <v>156800</v>
+        <v>161700</v>
       </c>
       <c r="J33" s="3">
-        <v>280300</v>
+        <v>331200</v>
       </c>
       <c r="K33" s="3">
         <v>-197600</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1398400</v>
+        <v>1398700</v>
       </c>
       <c r="E35" s="3">
-        <v>197800</v>
+        <v>203400</v>
       </c>
       <c r="F35" s="3">
-        <v>-77500</v>
+        <v>-86600</v>
       </c>
       <c r="G35" s="3">
-        <v>-457800</v>
+        <v>-497400</v>
       </c>
       <c r="H35" s="3">
-        <v>988400</v>
+        <v>1006900</v>
       </c>
       <c r="I35" s="3">
-        <v>156800</v>
+        <v>161700</v>
       </c>
       <c r="J35" s="3">
-        <v>280300</v>
+        <v>331200</v>
       </c>
       <c r="K35" s="3">
         <v>-197600</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5863600</v>
+        <v>5865500</v>
       </c>
       <c r="E41" s="3">
-        <v>2396700</v>
+        <v>2464800</v>
       </c>
       <c r="F41" s="3">
-        <v>2793900</v>
+        <v>3119700</v>
       </c>
       <c r="G41" s="3">
-        <v>2551200</v>
+        <v>2771800</v>
       </c>
       <c r="H41" s="3">
-        <v>2808700</v>
+        <v>2861300</v>
       </c>
       <c r="I41" s="3">
-        <v>3035300</v>
+        <v>3130400</v>
       </c>
       <c r="J41" s="3">
-        <v>2571900</v>
+        <v>2803700</v>
       </c>
       <c r="K41" s="3">
         <v>2545500</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2502100</v>
+        <v>2502900</v>
       </c>
       <c r="E42" s="3">
-        <v>3601300</v>
+        <v>3703700</v>
       </c>
       <c r="F42" s="3">
-        <v>4168200</v>
+        <v>4654200</v>
       </c>
       <c r="G42" s="3">
-        <v>3499100</v>
+        <v>3801700</v>
       </c>
       <c r="H42" s="3">
-        <v>3250700</v>
+        <v>3311600</v>
       </c>
       <c r="I42" s="3">
-        <v>5181400</v>
+        <v>5343800</v>
       </c>
       <c r="J42" s="3">
-        <v>3965800</v>
+        <v>4323200</v>
       </c>
       <c r="K42" s="3">
         <v>1948700</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2672800</v>
+        <v>2673700</v>
       </c>
       <c r="E43" s="3">
-        <v>1606600</v>
+        <v>1652300</v>
       </c>
       <c r="F43" s="3">
-        <v>1496400</v>
+        <v>1670800</v>
       </c>
       <c r="G43" s="3">
-        <v>1254600</v>
+        <v>1337700</v>
       </c>
       <c r="H43" s="3">
-        <v>1863300</v>
+        <v>1926900</v>
       </c>
       <c r="I43" s="3">
-        <v>1249200</v>
+        <v>1310300</v>
       </c>
       <c r="J43" s="3">
-        <v>1457900</v>
+        <v>878900</v>
       </c>
       <c r="K43" s="3">
         <v>787300</v>
@@ -2032,26 +2032,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1470800</v>
+        <v>1110400</v>
       </c>
       <c r="E45" s="3">
-        <v>1056500</v>
+        <v>836100</v>
       </c>
       <c r="F45" s="3">
-        <v>861400</v>
+        <v>709600</v>
       </c>
       <c r="G45" s="3">
-        <v>873500</v>
+        <v>702900</v>
       </c>
       <c r="H45" s="3">
-        <v>1657500</v>
+        <v>1339500</v>
       </c>
       <c r="I45" s="3">
-        <v>1727000</v>
+        <v>1083800</v>
       </c>
       <c r="J45" s="3">
-        <v>1946700</v>
+        <v>791800</v>
       </c>
       <c r="K45" s="3">
         <v>1058000</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12509400</v>
+        <v>12513500</v>
       </c>
       <c r="E46" s="3">
-        <v>8661100</v>
+        <v>8907200</v>
       </c>
       <c r="F46" s="3">
-        <v>9319900</v>
+        <v>10406400</v>
       </c>
       <c r="G46" s="3">
-        <v>8178400</v>
+        <v>8885700</v>
       </c>
       <c r="H46" s="3">
-        <v>9580300</v>
+        <v>9759600</v>
       </c>
       <c r="I46" s="3">
-        <v>11193000</v>
+        <v>11543700</v>
       </c>
       <c r="J46" s="3">
-        <v>8376700</v>
+        <v>9131800</v>
       </c>
       <c r="K46" s="3">
         <v>6339500</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6959800</v>
+        <v>6958500</v>
       </c>
       <c r="E47" s="3">
-        <v>7077500</v>
+        <v>7275000</v>
       </c>
       <c r="F47" s="3">
-        <v>6342100</v>
+        <v>7077600</v>
       </c>
       <c r="G47" s="3">
-        <v>6762500</v>
+        <v>7343500</v>
       </c>
       <c r="H47" s="3">
-        <v>7235700</v>
+        <v>7364500</v>
       </c>
       <c r="I47" s="3">
-        <v>3821000</v>
+        <v>3907400</v>
       </c>
       <c r="J47" s="3">
-        <v>7277700</v>
+        <v>3930400</v>
       </c>
       <c r="K47" s="3">
         <v>2947800</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>815300</v>
+        <v>815600</v>
       </c>
       <c r="E48" s="3">
-        <v>849100</v>
+        <v>873300</v>
       </c>
       <c r="F48" s="3">
-        <v>889700</v>
+        <v>993500</v>
       </c>
       <c r="G48" s="3">
-        <v>954000</v>
+        <v>1036500</v>
       </c>
       <c r="H48" s="3">
-        <v>1035100</v>
+        <v>1054400</v>
       </c>
       <c r="I48" s="3">
-        <v>827800</v>
+        <v>853800</v>
       </c>
       <c r="J48" s="3">
-        <v>1583400</v>
+        <v>863100</v>
       </c>
       <c r="K48" s="3">
         <v>772100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10152800</v>
+        <v>10156100</v>
       </c>
       <c r="E49" s="3">
-        <v>10173400</v>
+        <v>10462500</v>
       </c>
       <c r="F49" s="3">
-        <v>10206800</v>
+        <v>11396800</v>
       </c>
       <c r="G49" s="3">
-        <v>10248800</v>
+        <v>11135200</v>
       </c>
       <c r="H49" s="3">
-        <v>10090200</v>
+        <v>10279100</v>
       </c>
       <c r="I49" s="3">
-        <v>10128400</v>
+        <v>10445800</v>
       </c>
       <c r="J49" s="3">
-        <v>11820200</v>
+        <v>10772400</v>
       </c>
       <c r="K49" s="3">
         <v>9671100</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>456600</v>
+        <v>97000</v>
       </c>
       <c r="E52" s="3">
-        <v>263500</v>
+        <v>82600</v>
       </c>
       <c r="F52" s="3">
-        <v>289700</v>
+        <v>62300</v>
       </c>
       <c r="G52" s="3">
-        <v>254600</v>
+        <v>66800</v>
       </c>
       <c r="H52" s="3">
-        <v>278600</v>
+        <v>150200</v>
       </c>
       <c r="I52" s="3">
-        <v>228100</v>
+        <v>145000</v>
       </c>
       <c r="J52" s="3">
-        <v>183600</v>
+        <v>162600</v>
       </c>
       <c r="K52" s="3">
         <v>210200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>30893900</v>
+        <v>30904000</v>
       </c>
       <c r="E54" s="3">
-        <v>27024600</v>
+        <v>27792600</v>
       </c>
       <c r="F54" s="3">
-        <v>27048300</v>
+        <v>30201600</v>
       </c>
       <c r="G54" s="3">
-        <v>26398400</v>
+        <v>28681300</v>
       </c>
       <c r="H54" s="3">
-        <v>28219800</v>
+        <v>28747900</v>
       </c>
       <c r="I54" s="3">
-        <v>26198300</v>
+        <v>27019200</v>
       </c>
       <c r="J54" s="3">
-        <v>22872600</v>
+        <v>24934300</v>
       </c>
       <c r="K54" s="3">
         <v>19940700</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2320400</v>
+        <v>2363900</v>
       </c>
       <c r="E57" s="3">
-        <v>1067100</v>
+        <v>1120000</v>
       </c>
       <c r="F57" s="3">
-        <v>848600</v>
+        <v>969200</v>
       </c>
       <c r="G57" s="3">
-        <v>635300</v>
+        <v>727100</v>
       </c>
       <c r="H57" s="3">
-        <v>1733200</v>
+        <v>1797100</v>
       </c>
       <c r="I57" s="3">
-        <v>1651400</v>
+        <v>1703200</v>
       </c>
       <c r="J57" s="3">
-        <v>1051600</v>
+        <v>1146400</v>
       </c>
       <c r="K57" s="3">
         <v>1005100</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3645300</v>
+        <v>3666200</v>
       </c>
       <c r="E58" s="3">
-        <v>4606400</v>
+        <v>4777000</v>
       </c>
       <c r="F58" s="3">
-        <v>5620300</v>
+        <v>6332700</v>
       </c>
       <c r="G58" s="3">
-        <v>4746100</v>
+        <v>5219200</v>
       </c>
       <c r="H58" s="3">
-        <v>4302100</v>
+        <v>4445600</v>
       </c>
       <c r="I58" s="3">
-        <v>5076800</v>
+        <v>5235900</v>
       </c>
       <c r="J58" s="3">
-        <v>4600500</v>
+        <v>2507600</v>
       </c>
       <c r="K58" s="3">
         <v>951000</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4242800</v>
+        <v>2468000</v>
       </c>
       <c r="E59" s="3">
-        <v>2960000</v>
+        <v>1591100</v>
       </c>
       <c r="F59" s="3">
-        <v>2866500</v>
+        <v>1671100</v>
       </c>
       <c r="G59" s="3">
-        <v>2847500</v>
+        <v>1686300</v>
       </c>
       <c r="H59" s="3">
-        <v>3717900</v>
+        <v>2190500</v>
       </c>
       <c r="I59" s="3">
-        <v>2968900</v>
+        <v>1866800</v>
       </c>
       <c r="J59" s="3">
-        <v>3369700</v>
+        <v>1710400</v>
       </c>
       <c r="K59" s="3">
         <v>2227100</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10208500</v>
+        <v>10211800</v>
       </c>
       <c r="E60" s="3">
-        <v>8633500</v>
+        <v>8878800</v>
       </c>
       <c r="F60" s="3">
-        <v>9335400</v>
+        <v>10423800</v>
       </c>
       <c r="G60" s="3">
-        <v>8228900</v>
+        <v>8940500</v>
       </c>
       <c r="H60" s="3">
-        <v>9753300</v>
+        <v>9935800</v>
       </c>
       <c r="I60" s="3">
-        <v>9697200</v>
+        <v>10001000</v>
       </c>
       <c r="J60" s="3">
-        <v>5944000</v>
+        <v>6479800</v>
       </c>
       <c r="K60" s="3">
         <v>4183100</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2692600</v>
+        <v>2760700</v>
       </c>
       <c r="E61" s="3">
-        <v>1857700</v>
+        <v>1987900</v>
       </c>
       <c r="F61" s="3">
-        <v>1563900</v>
+        <v>1809200</v>
       </c>
       <c r="G61" s="3">
-        <v>3202800</v>
+        <v>3574400</v>
       </c>
       <c r="H61" s="3">
-        <v>2754300</v>
+        <v>2913400</v>
       </c>
       <c r="I61" s="3">
-        <v>3404100</v>
+        <v>3510800</v>
       </c>
       <c r="J61" s="3">
-        <v>4119400</v>
+        <v>4490800</v>
       </c>
       <c r="K61" s="3">
         <v>4784600</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>651500</v>
+        <v>45000</v>
       </c>
       <c r="E62" s="3">
-        <v>600000</v>
+        <v>34100</v>
       </c>
       <c r="F62" s="3">
-        <v>576900</v>
+        <v>26000</v>
       </c>
       <c r="G62" s="3">
-        <v>647800</v>
+        <v>61700</v>
       </c>
       <c r="H62" s="3">
-        <v>649200</v>
+        <v>37900</v>
       </c>
       <c r="I62" s="3">
-        <v>587500</v>
+        <v>47800</v>
       </c>
       <c r="J62" s="3">
-        <v>598200</v>
+        <v>53500</v>
       </c>
       <c r="K62" s="3">
         <v>545100</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13668400</v>
+        <v>13557000</v>
       </c>
       <c r="E66" s="3">
-        <v>11194900</v>
+        <v>11406400</v>
       </c>
       <c r="F66" s="3">
-        <v>11586000</v>
+        <v>12814100</v>
       </c>
       <c r="G66" s="3">
-        <v>12250500</v>
+        <v>13124100</v>
       </c>
       <c r="H66" s="3">
-        <v>13636600</v>
+        <v>13403000</v>
       </c>
       <c r="I66" s="3">
-        <v>13973200</v>
+        <v>14117700</v>
       </c>
       <c r="J66" s="3">
-        <v>10912400</v>
+        <v>11622600</v>
       </c>
       <c r="K66" s="3">
         <v>10062900</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4353200</v>
+        <v>4354600</v>
       </c>
       <c r="E72" s="3">
-        <v>2954900</v>
+        <v>3038900</v>
       </c>
       <c r="F72" s="3">
-        <v>2757100</v>
+        <v>3078600</v>
       </c>
       <c r="G72" s="3">
-        <v>2834700</v>
+        <v>3079800</v>
       </c>
       <c r="H72" s="3">
-        <v>3304300</v>
+        <v>3366100</v>
       </c>
       <c r="I72" s="3">
-        <v>2315900</v>
+        <v>2388400</v>
       </c>
       <c r="J72" s="3">
-        <v>2188200</v>
+        <v>1417300</v>
       </c>
       <c r="K72" s="3">
         <v>957900</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17225500</v>
+        <v>17231100</v>
       </c>
       <c r="E76" s="3">
-        <v>15829700</v>
+        <v>16279500</v>
       </c>
       <c r="F76" s="3">
-        <v>15462300</v>
+        <v>17264900</v>
       </c>
       <c r="G76" s="3">
-        <v>14147900</v>
+        <v>15371400</v>
       </c>
       <c r="H76" s="3">
-        <v>14583300</v>
+        <v>14856200</v>
       </c>
       <c r="I76" s="3">
-        <v>12225100</v>
+        <v>12608100</v>
       </c>
       <c r="J76" s="3">
-        <v>11960200</v>
+        <v>13038300</v>
       </c>
       <c r="K76" s="3">
         <v>9877800</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1398400</v>
+        <v>1398700</v>
       </c>
       <c r="E81" s="3">
-        <v>197800</v>
+        <v>203400</v>
       </c>
       <c r="F81" s="3">
-        <v>-77500</v>
+        <v>-86600</v>
       </c>
       <c r="G81" s="3">
-        <v>-457800</v>
+        <v>-497400</v>
       </c>
       <c r="H81" s="3">
-        <v>988400</v>
+        <v>1006900</v>
       </c>
       <c r="I81" s="3">
-        <v>156800</v>
+        <v>161700</v>
       </c>
       <c r="J81" s="3">
-        <v>280300</v>
+        <v>331200</v>
       </c>
       <c r="K81" s="3">
         <v>-197600</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>115200</v>
+        <v>121600</v>
       </c>
       <c r="E83" s="3">
-        <v>123400</v>
+        <v>151900</v>
       </c>
       <c r="F83" s="3">
-        <v>143900</v>
+        <v>175500</v>
       </c>
       <c r="G83" s="3">
-        <v>171600</v>
+        <v>174500</v>
       </c>
       <c r="H83" s="3">
-        <v>154500</v>
+        <v>145100</v>
       </c>
       <c r="I83" s="3">
-        <v>138400</v>
+        <v>79400</v>
       </c>
       <c r="J83" s="3">
-        <v>124500</v>
+        <v>75300</v>
       </c>
       <c r="K83" s="3">
         <v>99300</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3102100</v>
+        <v>3103100</v>
       </c>
       <c r="E89" s="3">
-        <v>372300</v>
+        <v>382900</v>
       </c>
       <c r="F89" s="3">
-        <v>348900</v>
+        <v>389600</v>
       </c>
       <c r="G89" s="3">
-        <v>-539000</v>
+        <v>-585600</v>
       </c>
       <c r="H89" s="3">
-        <v>1033800</v>
+        <v>1053200</v>
       </c>
       <c r="I89" s="3">
-        <v>1003100</v>
+        <v>1034500</v>
       </c>
       <c r="J89" s="3">
-        <v>996600</v>
+        <v>1086400</v>
       </c>
       <c r="K89" s="3">
         <v>728100</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-85400</v>
+        <v>-85500</v>
       </c>
       <c r="E91" s="3">
-        <v>-70100</v>
+        <v>-72100</v>
       </c>
       <c r="F91" s="3">
-        <v>-80400</v>
+        <v>-89700</v>
       </c>
       <c r="G91" s="3">
-        <v>-75000</v>
+        <v>-81500</v>
       </c>
       <c r="H91" s="3">
-        <v>-116000</v>
+        <v>-118200</v>
       </c>
       <c r="I91" s="3">
-        <v>-94900</v>
+        <v>-97900</v>
       </c>
       <c r="J91" s="3">
-        <v>-66400</v>
+        <v>-72400</v>
       </c>
       <c r="K91" s="3">
         <v>-94300</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>834500</v>
+        <v>834700</v>
       </c>
       <c r="E94" s="3">
-        <v>160200</v>
+        <v>164700</v>
       </c>
       <c r="F94" s="3">
-        <v>-584800</v>
+        <v>-653000</v>
       </c>
       <c r="G94" s="3">
-        <v>-538700</v>
+        <v>-585300</v>
       </c>
       <c r="H94" s="3">
-        <v>-340200</v>
+        <v>-346600</v>
       </c>
       <c r="I94" s="3">
-        <v>-1984700</v>
+        <v>-2046900</v>
       </c>
       <c r="J94" s="3">
-        <v>-2147400</v>
+        <v>-2340500</v>
       </c>
       <c r="K94" s="3">
         <v>-2737500</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-359100</v>
+        <v>-359200</v>
       </c>
       <c r="E100" s="3">
-        <v>-947000</v>
+        <v>-973900</v>
       </c>
       <c r="F100" s="3">
-        <v>552500</v>
+        <v>616900</v>
       </c>
       <c r="G100" s="3">
-        <v>849400</v>
+        <v>922900</v>
       </c>
       <c r="H100" s="3">
-        <v>-1304900</v>
+        <v>-1329300</v>
       </c>
       <c r="I100" s="3">
-        <v>1681300</v>
+        <v>1734000</v>
       </c>
       <c r="J100" s="3">
-        <v>1130500</v>
+        <v>1232600</v>
       </c>
       <c r="K100" s="3">
         <v>1697000</v>
@@ -4207,22 +4207,22 @@
         <v>16900</v>
       </c>
       <c r="E101" s="3">
-        <v>32600</v>
+        <v>33500</v>
       </c>
       <c r="F101" s="3">
-        <v>-65600</v>
+        <v>-73200</v>
       </c>
       <c r="G101" s="3">
-        <v>-100500</v>
+        <v>-109200</v>
       </c>
       <c r="H101" s="3">
-        <v>43600</v>
+        <v>44400</v>
       </c>
       <c r="I101" s="3">
-        <v>115500</v>
+        <v>119100</v>
       </c>
       <c r="J101" s="3">
-        <v>-6700</v>
+        <v>-7200</v>
       </c>
       <c r="K101" s="3">
         <v>204600</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3594400</v>
+        <v>3595600</v>
       </c>
       <c r="E102" s="3">
-        <v>-381900</v>
+        <v>-392800</v>
       </c>
       <c r="F102" s="3">
-        <v>251100</v>
+        <v>280400</v>
       </c>
       <c r="G102" s="3">
-        <v>-328800</v>
+        <v>-357200</v>
       </c>
       <c r="H102" s="3">
-        <v>-567700</v>
+        <v>-578400</v>
       </c>
       <c r="I102" s="3">
-        <v>815100</v>
+        <v>840700</v>
       </c>
       <c r="J102" s="3">
-        <v>-27000</v>
+        <v>-28700</v>
       </c>
       <c r="K102" s="3">
         <v>-107800</v>

--- a/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7301400</v>
+      </c>
+      <c r="E8" s="3">
         <v>6277100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2905400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3151900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2805500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5122300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4502200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4118200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2655100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1516900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1159000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>819400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>596700</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1368700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1145300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>654300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>723800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>617400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1058800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>919500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>719000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>653100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>423600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>331400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>211000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>148900</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5932800</v>
+      </c>
+      <c r="E10" s="3">
         <v>5131800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2251100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2428100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2188100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4063500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3582700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3399300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2002000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1093300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>827700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>608500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>447800</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1800100</v>
+      </c>
+      <c r="E12" s="3">
         <v>1709200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1209300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1415500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1174400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1532400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1398700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1269300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1061500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>458900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>366200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>189500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>130800</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,78 +960,84 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-148200</v>
+      </c>
+      <c r="E14" s="3">
         <v>141400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-313900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-54600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>65400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-573900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>246400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>5400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-600</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E15" s="3">
         <v>114800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>126400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>160200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>186000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>157000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>142300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>135200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5359200</v>
+      </c>
+      <c r="E17" s="3">
         <v>4680100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2892600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3374100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3023500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4398500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4123500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3665900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2878300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1463900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1188300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>691300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>502800</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1942300</v>
+      </c>
+      <c r="E18" s="3">
         <v>1597000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-222100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-218000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>723800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>378800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>452300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-223200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>53000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-29200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>128200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>93900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-543400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-173600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>114400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-19200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>235100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>102400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-85500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-119300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>81200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>407400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>76200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>54600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>42500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2597200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1885400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-42700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-267100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>778400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>606600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>706800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-42800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>504100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>75800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>201200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>150600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>237700</v>
+      </c>
+      <c r="E22" s="3">
         <v>291500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>219500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>246400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>262800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>240800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>219300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>197600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>101100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>42100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8700</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2716900</v>
+      </c>
+      <c r="E23" s="3">
         <v>1657300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>297100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-59000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-446300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1255200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>274700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>531600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-243000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>418300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>174100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>136400</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>356800</v>
+      </c>
+      <c r="E24" s="3">
         <v>246800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>98900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>42500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>54400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>250200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>115300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>197500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>66000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>65500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>44700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>42300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2360200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1410500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>198200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-101500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1005000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>159400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>334100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-309000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>352900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>129400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>94100</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2338200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1398700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>203400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-86600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-497400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1006900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>161700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>331200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-197600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>349100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>38300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>151900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>102500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>543400</v>
+      </c>
+      <c r="E32" s="3">
         <v>173600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-114400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>19200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-235100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-102400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>85500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>119300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-81200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-407400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-76200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-54600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-42500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2338200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1398700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>203400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-86600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-497400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1006900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>161700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>331200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-197600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>349100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>38300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>151900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>102500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2338200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1398700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>203400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-86600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-497400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1006900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>161700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>331200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-197600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>349100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>38300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>151900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>102500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,134 +1986,144 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6999900</v>
+      </c>
+      <c r="E41" s="3">
         <v>5865500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2464800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3119700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2771800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2861300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3130400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2803700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2545500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2674800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>836300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1085900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>981800</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3901200</v>
+      </c>
+      <c r="E42" s="3">
         <v>2502900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3703700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4654200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3801700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3311600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5343800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4323200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1948700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1146400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1015800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>553000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>202100</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1706900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2673700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1652300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1670800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1337700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1926900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1310300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>878900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>787300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>613200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>306400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>478000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>328400</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2053,8 +2148,8 @@
       <c r="J44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2068,219 +2163,237 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2752800</v>
+      </c>
+      <c r="E45" s="3">
         <v>1110400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>836100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>709600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>702900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1339500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1083800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>791800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1058000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1217200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>536400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>487600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>359800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15360800</v>
+      </c>
+      <c r="E46" s="3">
         <v>12513500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8907200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10406400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8885700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9759600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11543700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9131800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6339500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5651600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2694000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2185300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1096600</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6465700</v>
+      </c>
+      <c r="E47" s="3">
         <v>6958500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7275000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7077600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7343500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7364500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3907400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3930400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2947800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2087000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>950000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>926100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>412400</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>795700</v>
+      </c>
+      <c r="E48" s="3">
         <v>815600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>873300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>993500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1036500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1054400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>853800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>863100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>772100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>773400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>823600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>429900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>322500</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10104100</v>
+      </c>
+      <c r="E49" s="3">
         <v>10156100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10462500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11396800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11135200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10279100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10445800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10772400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9671100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7906700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>420500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>272800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>226200</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E52" s="3">
         <v>97000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>82600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>66800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>150200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>145000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>162600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>210200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>124200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>85100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>60400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33234400</v>
+      </c>
+      <c r="E54" s="3">
         <v>30904000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27792600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30201600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28681300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28747900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27019200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24934300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19940700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16542900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4923600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3166900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1674400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2271200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2363900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1120000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>969200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>727100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1797100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1703200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1146400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1005100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>827500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>363500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>249100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>146900</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2662400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3666200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4777000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6332700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5219200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4445600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5235900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2507600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>951000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1940900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>561700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>117800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>65100</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5206000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2468000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1591100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1671100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1686300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2190500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1866800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1710400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2227100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1917900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1080700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>399900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10139600</v>
+      </c>
+      <c r="E60" s="3">
         <v>10211800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8878800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10423800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8940500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9935800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10001000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6479800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4183100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4686300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2005900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>968700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>561000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2835300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2760700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1987900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1809200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3574400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2913400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3510800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4490800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4784600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2555000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1259600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>860600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>160900</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E62" s="3">
         <v>45000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>34100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>61700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>37900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>47800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>53500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>545100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>436700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13576900</v>
+      </c>
+      <c r="E66" s="3">
         <v>13557000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11406400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12814100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13124100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13403000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14117700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11622600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10062900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10341400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3420300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1869300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>743200</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="3">
         <v>4354600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3038900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3078600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3079800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3366100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2388400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1417300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>957900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1164800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>924500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>854500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>662700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19529800</v>
+      </c>
+      <c r="E76" s="3">
         <v>17231100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16279500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17264900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15371400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14856200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12608100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13038300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9877800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6201500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1503300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1297600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>931100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2338200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1398700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>203400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-86600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-497400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1006900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>161700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>331200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-197600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>349100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>38300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>151900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>102500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="3">
         <v>121600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>151900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>175500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>174500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>145100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>75300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>99300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>44000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>28700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>18400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3">
         <v>3103100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>382900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>389600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-585600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1053200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1034500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1086400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>728100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>424400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>309000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>373100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>237400</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="3">
         <v>-85500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-72100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-89700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-81500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-118200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-97900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-72400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-94300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-88800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-755500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-99100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-77900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3">
         <v>834700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>164700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-653000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-585300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-346600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2046900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2340500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2737500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-616200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1477600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-621600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-177900</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4029,9 +4262,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="3">
         <v>-359200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-973900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>616900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>922900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1329300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1734000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1232600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1697000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2120500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>855400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>808700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-74000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3">
         <v>16900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>33500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-73200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-109200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>44400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>119100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>204600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>23400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>3595600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-392800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>280400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-357200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-578400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>840700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-107800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1936900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-289900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>565400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -970,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-148200</v>
+        <v>-241000</v>
       </c>
       <c r="E14" s="3">
         <v>141400</v>
@@ -1015,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>111500</v>
+        <v>116200</v>
       </c>
       <c r="E15" s="3">
         <v>114800</v>
@@ -1185,7 +1185,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-543400</v>
+        <v>-427300</v>
       </c>
       <c r="E20" s="3">
         <v>-173600</v>
@@ -1230,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2597200</v>
+        <v>2485800</v>
       </c>
       <c r="E21" s="3">
         <v>1885400</v>
@@ -1725,7 +1725,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>543400</v>
+        <v>427300</v>
       </c>
       <c r="E32" s="3">
         <v>173600</v>
@@ -1993,7 +1993,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6999900</v>
+        <v>6636300</v>
       </c>
       <c r="E41" s="3">
         <v>5865500</v>
@@ -2083,7 +2083,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1706900</v>
+        <v>2992400</v>
       </c>
       <c r="E43" s="3">
         <v>2673700</v>
@@ -2173,7 +2173,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2752800</v>
+        <v>1444000</v>
       </c>
       <c r="E45" s="3">
         <v>1110400</v>
@@ -2661,7 +2661,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2271200</v>
+        <v>2325600</v>
       </c>
       <c r="E57" s="3">
         <v>2363900</v>
@@ -2706,7 +2706,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2662400</v>
+        <v>2689000</v>
       </c>
       <c r="E58" s="3">
         <v>3666200</v>
@@ -2751,7 +2751,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5206000</v>
+        <v>3182200</v>
       </c>
       <c r="E59" s="3">
         <v>2468000</v>
@@ -3309,8 +3309,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>10</v>
+      <c r="D72" s="3">
+        <v>6568600</v>
       </c>
       <c r="E72" s="3">
         <v>4354600</v>
@@ -3693,8 +3693,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>10</v>
+      <c r="D83" s="3">
+        <v>124800</v>
       </c>
       <c r="E83" s="3">
         <v>121600</v>
@@ -3963,8 +3963,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>10</v>
+      <c r="D89" s="3">
+        <v>2688700</v>
       </c>
       <c r="E89" s="3">
         <v>3103100</v>
@@ -4027,8 +4027,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>10</v>
+      <c r="D91" s="3">
+        <v>-81000</v>
       </c>
       <c r="E91" s="3">
         <v>-85500</v>
@@ -4162,8 +4162,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>10</v>
+      <c r="D94" s="3">
+        <v>-829100</v>
       </c>
       <c r="E94" s="3">
         <v>834700</v>
@@ -4406,8 +4406,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>10</v>
+      <c r="D100" s="3">
+        <v>-919300</v>
       </c>
       <c r="E100" s="3">
         <v>-359200</v>
@@ -4451,8 +4451,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>10</v>
+      <c r="D101" s="3">
+        <v>33800</v>
       </c>
       <c r="E101" s="3">
         <v>16900</v>
@@ -4497,7 +4497,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>974100</v>
       </c>
       <c r="E102" s="3">
         <v>3595600</v>

--- a/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCOM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8922700</v>
+      </c>
+      <c r="E8" s="3">
         <v>7301400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6277100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2905400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3151900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2805500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5122300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4502200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4118200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2655100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1516900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1159000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>819400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>596700</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1733100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1368700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1145300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>654300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>723800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>617400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1058800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>919500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>719000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>653100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>423600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>331400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>211000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>148900</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7189600</v>
+      </c>
+      <c r="E10" s="3">
         <v>5932800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5131800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2251100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2428100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2188100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4063500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3582700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3399300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2002000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1093300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>827700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>608500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>447800</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2164000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1800100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1709200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1209300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1415500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1174400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1532400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1398700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1269300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1061500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>458900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>366200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>189500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>130800</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,84 +979,90 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-2975500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-241000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>141400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-313900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-54600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>65400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-573900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>246400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6600</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>5400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-600</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E15" s="3">
         <v>116200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>114800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>126400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>160200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>186000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>157000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>142300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>135200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6667600</v>
+      </c>
+      <c r="E17" s="3">
         <v>5359200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4680100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2892600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3374100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3023500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4398500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4123500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3665900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2878300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1463900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1188300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>691300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>502800</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2255100</v>
+      </c>
+      <c r="E18" s="3">
         <v>1942300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1597000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-222100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-218000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>723800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>378800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>452300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-223200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>53000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-29200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>128200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>93900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-66100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-427300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-173600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>114400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-19200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>235100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>102400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-85500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-119300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>81200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>407400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>76200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>54600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>42500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2441400</v>
+      </c>
+      <c r="E21" s="3">
         <v>2485800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1885400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>24800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-42700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-267100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>778400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>606600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>706800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-42800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>504100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>75800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>201200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>150600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>121400</v>
+      </c>
+      <c r="E22" s="3">
         <v>237700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>291500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>219500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>246400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>262800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>240800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>219300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>197600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>101100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>42100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8700</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5604600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2716900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1657300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>297100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-59000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-446300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1255200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>274700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>531600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-243000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>418300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>174100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>136400</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>831400</v>
+      </c>
+      <c r="E24" s="3">
         <v>356800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>246800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>98900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>42500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>54400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>250200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>115300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>197500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>66000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>44700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>42300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4773200</v>
+      </c>
+      <c r="E26" s="3">
         <v>2360200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1410500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>198200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-101500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-500700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1005000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>159400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>334100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-309000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>352900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>129400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>94100</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4760100</v>
+      </c>
+      <c r="E27" s="3">
         <v>2338200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1398700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>203400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-86600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-497400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1006900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>161700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>331200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-197600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>349100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>38300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>151900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>102500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E32" s="3">
         <v>427300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>173600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-114400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>19200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-235100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-102400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>85500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>119300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-81200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-407400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-76200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-54600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4760100</v>
+      </c>
+      <c r="E33" s="3">
         <v>2338200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1398700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>203400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-86600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-497400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1006900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>161700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>331200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-197600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>349100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>38300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>151900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>102500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4760100</v>
+      </c>
+      <c r="E35" s="3">
         <v>2338200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1398700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>203400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-86600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-497400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1006900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>161700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>331200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-197600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>349100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>38300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>151900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>102500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,143 +2072,153 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5697100</v>
+      </c>
+      <c r="E41" s="3">
         <v>6636300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5865500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2464800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3119700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2771800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2861300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3130400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2803700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2545500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2674800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>836300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1085900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>981800</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4576100</v>
+      </c>
+      <c r="E42" s="3">
         <v>3901200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2502900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3703700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4654200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3801700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3311600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5343800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4323200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1948700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1146400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1015800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>553000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>202100</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3745300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2992400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2673700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1652300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1670800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1337700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1926900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1310300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>878900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>787300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>613200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>306400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>478000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>328400</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2151,8 +2246,8 @@
       <c r="K44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2166,234 +2261,252 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2311000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1444000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1110400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>836100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>709600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>702900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1339500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1083800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>791800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1058000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1217200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>536400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>487600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>359800</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17306700</v>
+      </c>
+      <c r="E46" s="3">
         <v>15360800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12513500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8907200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10406400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8885700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9759600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11543700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9131800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6339500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5651600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2694000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2185300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1096600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8774900</v>
+      </c>
+      <c r="E47" s="3">
         <v>6465700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6958500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7275000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7077600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7343500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7364500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3907400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3930400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2947800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2087000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>950000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>926100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>412400</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>904400</v>
+      </c>
+      <c r="E48" s="3">
         <v>795700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>815600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>873300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>993500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1036500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1054400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>853800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>863100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>772100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>773400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>823600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>429900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>322500</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10763000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10104100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10156100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10462500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11396800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11135200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10279100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10445800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10772400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9671100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7906700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>420500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>272800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>226200</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E52" s="3">
         <v>62200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>97000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>82600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>62300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>66800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>150200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>145000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>162600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>210200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>124200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>85100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>60400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>38228700</v>
+      </c>
+      <c r="E54" s="3">
         <v>33234400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30904000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27792600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30201600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28681300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28747900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27019200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24934300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19940700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16542900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4923600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3166900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1674400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2787100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2325600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2363900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1120000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>969200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>727100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1797100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1703200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1146400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1005100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>827500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>363500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>249100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>146900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2802100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2689000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3666200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4777000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6332700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5219200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4445600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5235900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2507600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>951000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1940900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>561700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>117800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>65100</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3234600</v>
+      </c>
+      <c r="E59" s="3">
         <v>3182200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2468000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1591100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1671100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1686300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2190500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1866800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1710400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2227100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1917900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1080700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>700100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>399900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11175900</v>
+      </c>
+      <c r="E60" s="3">
         <v>10139600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10211800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8878800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10423800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8940500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9935800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10001000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6479800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4183100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4686300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2005900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>968700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>561000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1717800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2835300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2760700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1987900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1809200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3574400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2913400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3510800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4490800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4784600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2555000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1259600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>860600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>160900</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E62" s="3">
         <v>40600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>45000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>61700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>37900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>47800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>545100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>436700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13551800</v>
+      </c>
+      <c r="E66" s="3">
         <v>13576900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13557000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11406400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12814100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13124100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13403000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14117700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11622600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10062900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10341400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3420300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1869300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>743200</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11411400</v>
+      </c>
+      <c r="E72" s="3">
         <v>6568600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4354600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3038900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3078600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3079800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3366100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2388400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1417300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>957900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1164800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>924500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>854500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>662700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24440800</v>
+      </c>
+      <c r="E76" s="3">
         <v>19529800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17231100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16279500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17264900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15371400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14856200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12608100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13038300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9877800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6201500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1503300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1297600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>931100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4760100</v>
+      </c>
+      <c r="E81" s="3">
         <v>2338200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1398700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>203400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-86600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-497400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1006900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>161700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>331200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-197600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>349100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>38300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>151900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>102500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E83" s="3">
         <v>124800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>121600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>151900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>175500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>174500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>145100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>79400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>75300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>99300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>44000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>28700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>18400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14200</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2055800</v>
+      </c>
+      <c r="E89" s="3">
         <v>2688700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3103100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>382900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>389600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-585600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1053200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1034500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1086400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>728100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>424400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>309000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>373100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>237400</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-113900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-85500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-72100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-89700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-81500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-118200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-97900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-72400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-94300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-88800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-755500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-99100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-77900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-597800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-829100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>834700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>164700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-653000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-585300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-346600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2046900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2340500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2737500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-616200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1477600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-621600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-177900</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,13 +4453,14 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>203400</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2096400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-919300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-359200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-973900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>616900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>922900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1329300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1734000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1232600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1697000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2120500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>855400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>808700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E101" s="3">
         <v>33800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>16900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>33500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-73200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-109200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>44400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>119100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>204600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>23400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-663700</v>
+      </c>
+      <c r="E102" s="3">
         <v>974100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3595600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-392800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>280400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-357200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-578400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>840700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-107800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1936900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-289900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>565400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
